--- a/data/Genealogie_MEME.xlsx
+++ b/data/Genealogie_MEME.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="75" windowWidth="18195" windowHeight="11820" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="75" windowWidth="18195" windowHeight="11820" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feuille1" sheetId="1" state="visible" r:id="rId1"/>
@@ -604,6 +604,219 @@
   </si>
   <si>
     <t>Lantriac</t>
+  </si>
+  <si>
+    <t>Frère et soeur</t>
+  </si>
+  <si>
+    <t>P022</t>
+  </si>
+  <si>
+    <t>Jean-Jacques</t>
+  </si>
+  <si>
+    <t>Elisabeth</t>
+  </si>
+  <si>
+    <t>Marguerite</t>
+  </si>
+  <si>
+    <t>Marie</t>
+  </si>
+  <si>
+    <t>Ph</t>
+  </si>
+  <si>
+    <t>Philomène</t>
+  </si>
+  <si>
+    <t>P023</t>
+  </si>
+  <si>
+    <t>P024</t>
+  </si>
+  <si>
+    <t>P025</t>
+  </si>
+  <si>
+    <t>P026</t>
+  </si>
+  <si>
+    <t>P027</t>
+  </si>
+  <si>
+    <t>Elise Jeanne Marie</t>
+  </si>
+  <si>
+    <t>D005</t>
+  </si>
+  <si>
+    <t>P0</t>
+  </si>
+  <si>
+    <t>P023;P024;P025;P026;P027</t>
+  </si>
+  <si>
+    <t>Tonton du PEPE</t>
+  </si>
+  <si>
+    <t>à confirmer</t>
+  </si>
+  <si>
+    <t>P022;P024;P025;P026;P027</t>
+  </si>
+  <si>
+    <t>P022;P023;P025;P026;P027</t>
+  </si>
+  <si>
+    <t>P022;P023;P024;P026;P027</t>
+  </si>
+  <si>
+    <t>P022;P023;P024;P025;P027</t>
+  </si>
+  <si>
+    <t>P022;P023;P024;P025;P026</t>
+  </si>
+  <si>
+    <t>Tatan du PEPE ou Maman du PEPE</t>
+  </si>
+  <si>
+    <t>Tantan ou Maman du PEPE la maman Elise si tatan Elisabeth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tatan du PEPE  </t>
+  </si>
+  <si>
+    <t>Tatan du PEPE</t>
+  </si>
+  <si>
+    <t>Maréchal à Perret commune de ARAULES</t>
+  </si>
+  <si>
+    <t>commune d'Annonay</t>
+  </si>
+  <si>
+    <t>célibataire pont de l'enceinte commune d'Yssingeaux</t>
+  </si>
+  <si>
+    <t>chapteuil commune de St Julien Chapteuil</t>
+  </si>
+  <si>
+    <t>maréchal à Combvieille commune d'ARAULES</t>
+  </si>
+  <si>
+    <t>chapteuil commune de St JULIEN CHAPTEUIL</t>
+  </si>
+  <si>
+    <t>célibataire pont de l'enceinte commune d'YSSINGEAUX</t>
+  </si>
+  <si>
+    <t>commune d'ANNONAY</t>
+  </si>
+  <si>
+    <t>assistée autorisé de son époux Pierre BESSON Pont de l'enceinte commune d'YSSINGEAUX</t>
+  </si>
+  <si>
+    <t>P028</t>
+  </si>
+  <si>
+    <t>Jacques</t>
+  </si>
+  <si>
+    <t>Père des tantes et oncle du PEPE</t>
+  </si>
+  <si>
+    <t>30 avril 1887</t>
+  </si>
+  <si>
+    <t>BESSIERES</t>
+  </si>
+  <si>
+    <t>janvier 1890</t>
+  </si>
+  <si>
+    <t>P029</t>
+  </si>
+  <si>
+    <t>Mères des tantes et oncles du PEPE</t>
+  </si>
+  <si>
+    <t>Père des tantes et oncles du PEPE</t>
+  </si>
+  <si>
+    <t>ainé de la fraterie</t>
+  </si>
+  <si>
+    <t>second fils</t>
+  </si>
+  <si>
+    <t>P030</t>
+  </si>
+  <si>
+    <t>P022;P023;P024;P025;P026;P027</t>
+  </si>
+  <si>
+    <t>P023;P024;P025;P026;P027;P028</t>
+  </si>
+  <si>
+    <t>P022;P024;P025;P026;P027;P028</t>
+  </si>
+  <si>
+    <t>P022;P023;P025;P026;P027;P028</t>
+  </si>
+  <si>
+    <t>P022;P023;P024;P026;P027;P028</t>
+  </si>
+  <si>
+    <t>P022;P023;P024;P025;P027;P028</t>
+  </si>
+  <si>
+    <t>P022;P023;P024;P025;P026;P028</t>
+  </si>
+  <si>
+    <t>décédé à St JULIEN CHAPTEUIL en 1899</t>
+  </si>
+  <si>
+    <t>Françoise</t>
+  </si>
+  <si>
+    <t>novembre 1899</t>
+  </si>
+  <si>
+    <t>SAINT JULIEN CHAPTEUIL</t>
+  </si>
+  <si>
+    <t>ARAULES</t>
+  </si>
+  <si>
+    <t>P003</t>
+  </si>
+  <si>
+    <t>Pierre Joannes Antoine</t>
+  </si>
+  <si>
+    <t>P02</t>
+  </si>
+  <si>
+    <t>D006</t>
+  </si>
+  <si>
+    <t>BERTHOLON Jean Pierre</t>
+  </si>
+  <si>
+    <t>BERTHOLON Pierre Joannès</t>
+  </si>
+  <si>
+    <t>D00</t>
+  </si>
+  <si>
+    <t>Même père et mère du PEPE</t>
+  </si>
+  <si>
+    <t>St Etienne</t>
+  </si>
+  <si>
+    <t>Elise LAULAGNIER/BERTHOLON</t>
   </si>
 </sst>
 </file>
@@ -1140,8 +1353,8 @@
     <col width="26.36328125" bestFit="1" customWidth="1" min="5" max="5"/>
     <col width="14.36328125" bestFit="1" customWidth="1" min="6" max="6"/>
     <col width="29.453125" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="18.7265625" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="16" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="57" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="13.81640625" bestFit="1" customWidth="1" min="9" max="9"/>
     <col width="11.7265625" bestFit="1" customWidth="1" min="10" max="10"/>
     <col width="11.7265625" bestFit="1" customWidth="1" min="11" max="11"/>
     <col width="15.7265625" bestFit="1" customWidth="1" min="12" max="12"/>
@@ -1307,7 +1520,9 @@
         <v>156</v>
       </c>
       <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>266</v>
+      </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -1358,19 +1573,19 @@
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>164</v>
+        <v>261</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
         <v>165</v>
       </c>
       <c r="J4" s="12">
-        <v>19195</v>
+        <v>11570</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2" t="s">
-        <v>166</v>
+        <v>265</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1452,7 +1667,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>190</v>
@@ -1473,14 +1688,16 @@
       <c r="H6" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="12">
+      <c r="I6" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="J6" s="12">
         <v>823</v>
       </c>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
       <c r="M6" s="2" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1503,22 +1720,40 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>163</v>
+      </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="G7" s="2" t="s">
+        <v>262</v>
+      </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+      <c r="J7" s="12">
+        <v>19195</v>
+      </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
+      <c r="M7" s="2" t="s">
+        <v>166</v>
+      </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
+      <c r="P7" s="2" t="s">
+        <v>167</v>
+      </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
@@ -6946,25 +7181,25 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:W200"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" defaultColWidth="8.7265625"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1" style="16"/>
-    <col width="16" customWidth="1" min="2" max="2" style="16"/>
+    <col width="11.6328125" customWidth="1" min="1" max="1" style="16" bestFit="1"/>
+    <col width="20.08984375" customWidth="1" min="2" max="2" style="16" bestFit="1"/>
     <col width="16" customWidth="1" min="3" max="3" style="16"/>
     <col width="20" customWidth="1" min="4" max="4" style="16"/>
     <col width="5.36328125" customWidth="1" min="5" max="5" bestFit="1" style="16"/>
     <col width="16.81640625" customWidth="1" min="6" max="6" style="16" bestFit="1"/>
-    <col width="5.1796875" customWidth="1" min="7" max="7" style="16"/>
+    <col width="15.1796875" customWidth="1" min="7" max="7" style="16" bestFit="1"/>
     <col width="25.54296875" customWidth="1" min="8" max="8" bestFit="1" style="16"/>
     <col width="14" customWidth="1" min="9" max="9" style="16"/>
-    <col width="5.90625" customWidth="1" min="10" max="10" style="16"/>
+    <col width="13.81640625" customWidth="1" min="10" max="10" style="16" bestFit="1"/>
     <col width="16" customWidth="1" min="11" max="11" style="16"/>
     <col width="16" customWidth="1" min="12" max="12" style="16"/>
     <col width="16" customWidth="1" min="13" max="13" style="16"/>
     <col width="9.54296875" customWidth="1" min="14" max="14" style="16"/>
-    <col width="16" customWidth="1" min="15" max="15" style="16"/>
+    <col width="29.08984375" customWidth="1" min="15" max="15" style="16" bestFit="1"/>
     <col width="9.54296875" customWidth="1" min="16" max="16" bestFit="1" style="16"/>
-    <col width="21.54296875" customWidth="1" min="17" max="17" style="16" bestFit="1"/>
+    <col width="30.54296875" customWidth="1" min="17" max="17" style="16" bestFit="1"/>
     <col width="18" customWidth="1" min="18" max="18" style="16"/>
     <col width="16" customWidth="1" min="19" max="19" style="16"/>
     <col width="30" customWidth="1" min="20" max="20" style="16"/>
@@ -7157,60 +7392,69 @@
     </row>
     <row r="4" customFormat="1" s="16">
       <c r="A4" s="17" t="s">
-        <v>113</v>
+        <v>257</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>123</v>
+        <v>258</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D4" s="17"/>
       <c r="E4" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="F4" s="19"/>
+      <c r="F4" s="19">
+        <v>12222</v>
+      </c>
       <c r="G4" s="19"/>
-      <c r="H4" s="17"/>
+      <c r="H4" s="17" t="s">
+        <v>175</v>
+      </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
       <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
+      <c r="L4" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="M4" s="17" t="s">
+        <v>121</v>
+      </c>
       <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
+      <c r="O4" s="17" t="s">
+        <v>259</v>
+      </c>
       <c r="P4" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="17" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>58</v>
+        <v>214</v>
       </c>
       <c r="S4" s="17" t="s">
-        <v>133</v>
+        <v>260</v>
       </c>
       <c r="T4" s="17"/>
       <c r="U4" s="17"/>
-      <c r="V4" s="17"/>
-      <c r="W4" s="17"/>
+      <c r="V4" s="17" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="5" customFormat="1" s="16">
       <c r="A5" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>124</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="D5" s="17"/>
       <c r="E5" s="17" t="s">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="F5" s="19"/>
       <c r="G5" s="19"/>
@@ -7226,7 +7470,7 @@
         <v>2</v>
       </c>
       <c r="Q5" s="17" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="R5" s="17" t="s">
         <v>58</v>
@@ -7241,27 +7485,23 @@
     </row>
     <row r="6" customFormat="1" s="16">
       <c r="A6" s="17" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="17" t="s">
-        <v>174</v>
-      </c>
+      <c r="F6" s="19"/>
       <c r="G6" s="19"/>
-      <c r="H6" s="17" t="s">
-        <v>150</v>
-      </c>
+      <c r="H6" s="17"/>
       <c r="I6" s="19"/>
       <c r="J6" s="19"/>
       <c r="K6" s="17"/>
@@ -7273,13 +7513,13 @@
         <v>2</v>
       </c>
       <c r="Q6" s="17" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="R6" s="17" t="s">
         <v>58</v>
       </c>
       <c r="S6" s="17" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="T6" s="17"/>
       <c r="U6" s="17"/>
@@ -7288,24 +7528,26 @@
     </row>
     <row r="7" customFormat="1" s="16">
       <c r="A7" s="17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>172</v>
+        <v>209</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="17"/>
+      <c r="D7" s="17" t="s">
+        <v>144</v>
+      </c>
       <c r="E7" s="17" t="s">
-        <v>117</v>
+        <v>51</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G7" s="19"/>
       <c r="H7" s="17" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="I7" s="19"/>
       <c r="J7" s="19"/>
@@ -7318,13 +7560,13 @@
         <v>2</v>
       </c>
       <c r="Q7" s="17" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="R7" s="17" t="s">
         <v>58</v>
       </c>
       <c r="S7" s="17" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="T7" s="17"/>
       <c r="U7" s="17"/>
@@ -7332,14 +7574,26 @@
       <c r="W7" s="17"/>
     </row>
     <row r="8" customFormat="1" s="16">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
+      <c r="A8" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>109</v>
+      </c>
       <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="19"/>
+      <c r="E8" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>173</v>
+      </c>
       <c r="G8" s="19"/>
-      <c r="H8" s="17"/>
+      <c r="H8" s="17" t="s">
+        <v>176</v>
+      </c>
       <c r="I8" s="19"/>
       <c r="J8" s="19"/>
       <c r="K8" s="17"/>
@@ -7347,210 +7601,414 @@
       <c r="M8" s="17"/>
       <c r="N8" s="17"/>
       <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="17"/>
-      <c r="S8" s="17"/>
+      <c r="P8" s="17">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="R8" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="S8" s="17" t="s">
+        <v>161</v>
+      </c>
       <c r="T8" s="17"/>
       <c r="U8" s="17"/>
       <c r="V8" s="17"/>
       <c r="W8" s="17"/>
     </row>
     <row r="9" customFormat="1" s="16">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
+      <c r="A9" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>144</v>
+      </c>
       <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+      <c r="E9" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
+      <c r="G9" s="19" t="s">
+        <v>242</v>
+      </c>
       <c r="H9" s="17"/>
       <c r="I9" s="19"/>
       <c r="J9" s="19"/>
       <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
+      <c r="L9" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="M9" s="17" t="s">
+        <v>244</v>
+      </c>
       <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="17"/>
-      <c r="S9" s="17"/>
+      <c r="O9" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="P9" s="17">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="R9" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="S9" s="17" t="s">
+        <v>210</v>
+      </c>
       <c r="T9" s="17"/>
       <c r="U9" s="17"/>
-      <c r="V9" s="17"/>
+      <c r="V9" s="17" t="s">
+        <v>224</v>
+      </c>
       <c r="W9" s="17"/>
     </row>
     <row r="10" customFormat="1" s="16">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
+      <c r="A10" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>144</v>
+      </c>
       <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
+      <c r="E10" s="17" t="s">
+        <v>51</v>
+      </c>
       <c r="F10" s="19"/>
       <c r="G10" s="19"/>
       <c r="H10" s="17"/>
       <c r="I10" s="19"/>
       <c r="J10" s="19"/>
       <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
+      <c r="L10" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="M10" s="17" t="s">
+        <v>244</v>
+      </c>
       <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="17"/>
-      <c r="T10" s="17"/>
+      <c r="O10" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="P10" s="17">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="R10" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="S10" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="T10" s="17" t="s">
+        <v>221</v>
+      </c>
       <c r="U10" s="17"/>
-      <c r="V10" s="17"/>
+      <c r="V10" s="17" t="s">
+        <v>231</v>
+      </c>
       <c r="W10" s="17"/>
     </row>
     <row r="11" customFormat="1" s="16">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
+      <c r="A11" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>144</v>
+      </c>
       <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+      <c r="E11" s="17" t="s">
+        <v>51</v>
+      </c>
       <c r="F11" s="19"/>
       <c r="G11" s="19"/>
       <c r="H11" s="17"/>
       <c r="I11" s="19"/>
       <c r="J11" s="19"/>
       <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
+      <c r="L11" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="M11" s="17" t="s">
+        <v>244</v>
+      </c>
       <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="17"/>
-      <c r="S11" s="17"/>
+      <c r="O11" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="P11" s="17">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="R11" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="S11" s="17" t="s">
+        <v>210</v>
+      </c>
       <c r="T11" s="17"/>
       <c r="U11" s="17"/>
-      <c r="V11" s="17"/>
+      <c r="V11" s="17" t="s">
+        <v>230</v>
+      </c>
       <c r="W11" s="17"/>
     </row>
     <row r="12" customFormat="1" s="16">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
+      <c r="A12" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>144</v>
+      </c>
       <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
+      <c r="E12" s="17" t="s">
+        <v>51</v>
+      </c>
       <c r="F12" s="19"/>
       <c r="G12" s="19"/>
       <c r="H12" s="17"/>
       <c r="I12" s="19"/>
       <c r="J12" s="19"/>
       <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
+      <c r="L12" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="M12" s="17" t="s">
+        <v>244</v>
+      </c>
       <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="17"/>
+      <c r="O12" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="P12" s="17">
+        <v>2</v>
+      </c>
+      <c r="Q12" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="R12" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="S12" s="17" t="s">
+        <v>210</v>
+      </c>
       <c r="T12" s="17"/>
       <c r="U12" s="17"/>
-      <c r="V12" s="17"/>
+      <c r="V12" s="17" t="s">
+        <v>229</v>
+      </c>
       <c r="W12" s="17"/>
     </row>
     <row r="13" customFormat="1" s="16">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
+      <c r="A13" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>144</v>
+      </c>
       <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
+      <c r="E13" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
+      <c r="G13" s="19" t="s">
+        <v>243</v>
+      </c>
       <c r="H13" s="17"/>
       <c r="I13" s="19"/>
       <c r="J13" s="19"/>
       <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
+      <c r="L13" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="M13" s="17" t="s">
+        <v>244</v>
+      </c>
       <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="17"/>
+      <c r="O13" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="P13" s="17">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="R13" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="S13" s="17" t="s">
+        <v>210</v>
+      </c>
       <c r="T13" s="17"/>
       <c r="U13" s="17"/>
-      <c r="V13" s="17"/>
+      <c r="V13" s="17" t="s">
+        <v>228</v>
+      </c>
       <c r="W13" s="17"/>
     </row>
     <row r="14" customFormat="1" s="16">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
+      <c r="A14" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>144</v>
+      </c>
       <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
+      <c r="E14" s="17" t="s">
+        <v>51</v>
+      </c>
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
       <c r="H14" s="17"/>
       <c r="I14" s="19"/>
       <c r="J14" s="19"/>
       <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
+      <c r="L14" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="M14" s="17" t="s">
+        <v>244</v>
+      </c>
       <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="17"/>
-      <c r="S14" s="17"/>
+      <c r="O14" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="P14" s="17">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="R14" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="S14" s="17" t="s">
+        <v>210</v>
+      </c>
       <c r="T14" s="17"/>
       <c r="U14" s="17"/>
-      <c r="V14" s="17"/>
+      <c r="V14" s="17" t="s">
+        <v>232</v>
+      </c>
       <c r="W14" s="17"/>
     </row>
     <row r="15" customFormat="1" s="16">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
+      <c r="A15" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>144</v>
+      </c>
       <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
+      <c r="E15" s="17" t="s">
+        <v>51</v>
+      </c>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
       <c r="H15" s="17"/>
       <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
+      <c r="J15" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="L15" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="M15" s="17" t="s">
+        <v>244</v>
+      </c>
       <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="17"/>
-      <c r="S15" s="17"/>
+      <c r="O15" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="P15" s="17">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="R15" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="S15" s="17" t="s">
+        <v>210</v>
+      </c>
       <c r="T15" s="17"/>
       <c r="U15" s="17"/>
-      <c r="V15" s="17"/>
+      <c r="V15" s="17" t="s">
+        <v>252</v>
+      </c>
       <c r="W15" s="17"/>
     </row>
     <row r="16" customFormat="1" s="16">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
+      <c r="A16" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>144</v>
+      </c>
       <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
+      <c r="E16" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="F16" s="19"/>
       <c r="G16" s="19"/>
       <c r="H16" s="17"/>
-      <c r="I16" s="19"/>
+      <c r="I16" s="17" t="s">
+        <v>236</v>
+      </c>
       <c r="J16" s="19"/>
       <c r="K16" s="17"/>
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
       <c r="N16" s="17"/>
       <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="17"/>
+      <c r="P16" s="17">
+        <v>3</v>
+      </c>
+      <c r="Q16" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="R16" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="S16" s="17" t="s">
+        <v>210</v>
+      </c>
       <c r="T16" s="17"/>
       <c r="U16" s="17"/>
       <c r="V16" s="17"/>
@@ -7558,22 +8016,34 @@
     </row>
     <row r="17" customFormat="1" s="16">
       <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>237</v>
+      </c>
       <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
+      <c r="E17" s="17" t="s">
+        <v>51</v>
+      </c>
       <c r="F17" s="19"/>
       <c r="G17" s="19"/>
       <c r="H17" s="17"/>
       <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
+      <c r="J17" s="19" t="s">
+        <v>238</v>
+      </c>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
+      <c r="P17" s="17">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="17" t="s">
+        <v>240</v>
+      </c>
       <c r="R17" s="17"/>
       <c r="S17" s="17"/>
       <c r="T17" s="17"/>
@@ -12155,6 +12625,56 @@
       <c r="U200" s="17"/>
       <c r="V200" s="17"/>
       <c r="W200" s="17"/>
+    </row>
+    <row r="201" customFormat="1" s="16">
+      <c r="A201" s="17"/>
+      <c r="B201" s="17"/>
+      <c r="C201" s="17"/>
+      <c r="D201" s="17"/>
+      <c r="E201" s="17"/>
+      <c r="F201" s="19"/>
+      <c r="G201" s="19"/>
+      <c r="H201" s="17"/>
+      <c r="I201" s="19"/>
+      <c r="J201" s="19"/>
+      <c r="K201" s="17"/>
+      <c r="L201" s="17"/>
+      <c r="M201" s="17"/>
+      <c r="N201" s="17"/>
+      <c r="O201" s="17"/>
+      <c r="P201" s="17"/>
+      <c r="Q201" s="17"/>
+      <c r="R201" s="17"/>
+      <c r="S201" s="17"/>
+      <c r="T201" s="17"/>
+      <c r="U201" s="17"/>
+      <c r="V201" s="17"/>
+      <c r="W201" s="17"/>
+    </row>
+    <row r="202" customFormat="1" s="16">
+      <c r="A202" s="17"/>
+      <c r="B202" s="17"/>
+      <c r="C202" s="17"/>
+      <c r="D202" s="17"/>
+      <c r="E202" s="17"/>
+      <c r="F202" s="19"/>
+      <c r="G202" s="19"/>
+      <c r="H202" s="17"/>
+      <c r="I202" s="19"/>
+      <c r="J202" s="19"/>
+      <c r="K202" s="17"/>
+      <c r="L202" s="17"/>
+      <c r="M202" s="17"/>
+      <c r="N202" s="17"/>
+      <c r="O202" s="17"/>
+      <c r="P202" s="17"/>
+      <c r="Q202" s="17"/>
+      <c r="R202" s="17"/>
+      <c r="S202" s="17"/>
+      <c r="T202" s="17"/>
+      <c r="U202" s="17"/>
+      <c r="V202" s="17"/>
+      <c r="W202" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Genealogie_MEME.xlsx
+++ b/data/Genealogie_MEME.xlsx
@@ -817,6 +817,21 @@
   </si>
   <si>
     <t>Elise LAULAGNIER/BERTHOLON</t>
+  </si>
+  <si>
+    <t>16 juin 1913</t>
+  </si>
+  <si>
+    <t>8 novembre 1910</t>
+  </si>
+  <si>
+    <t>17 juin 1933</t>
+  </si>
+  <si>
+    <t>12 mars 1994</t>
+  </si>
+  <si>
+    <t>14 juillet 1971</t>
   </si>
 </sst>
 </file>
@@ -923,7 +938,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -964,6 +979,15 @@
       <alignment/>
     </xf>
     <xf numFmtId="164" applyNumberFormat="1" fontId="7" applyFont="1" fillId="3" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" applyFont="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="9" applyFont="1" fillId="2" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment wrapText="1" vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="7" applyFont="1" fillId="3" applyFill="1" applyAlignment="1" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -7188,11 +7212,11 @@
     <col width="16" customWidth="1" min="3" max="3" style="16"/>
     <col width="20" customWidth="1" min="4" max="4" style="16"/>
     <col width="5.36328125" customWidth="1" min="5" max="5" bestFit="1" style="16"/>
-    <col width="16.81640625" customWidth="1" min="6" max="6" style="16" bestFit="1"/>
-    <col width="15.1796875" customWidth="1" min="7" max="7" style="16" bestFit="1"/>
+    <col width="16.81640625" customWidth="1" min="6" max="6" style="20" bestFit="1"/>
+    <col width="15.1796875" customWidth="1" min="7" max="7" style="20" bestFit="1"/>
     <col width="25.54296875" customWidth="1" min="8" max="8" bestFit="1" style="16"/>
-    <col width="14" customWidth="1" min="9" max="9" style="16"/>
-    <col width="13.81640625" customWidth="1" min="10" max="10" style="16" bestFit="1"/>
+    <col width="14" customWidth="1" min="9" max="9" style="20"/>
+    <col width="13.81640625" customWidth="1" min="10" max="10" style="20" bestFit="1"/>
     <col width="16" customWidth="1" min="11" max="11" style="16"/>
     <col width="16" customWidth="1" min="12" max="12" style="16"/>
     <col width="16" customWidth="1" min="13" max="13" style="16"/>
@@ -7225,19 +7249,19 @@
       <c r="E1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="21" t="s">
         <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="21" t="s">
         <v>35</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -7296,17 +7320,17 @@
       <c r="E2" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="19">
-        <v>4916</v>
-      </c>
-      <c r="G2" s="19"/>
+      <c r="F2" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="G2" s="22"/>
       <c r="H2" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="I2" s="19">
-        <v>34405</v>
-      </c>
-      <c r="J2" s="19"/>
+      <c r="I2" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="J2" s="22"/>
       <c r="K2" s="17" t="s">
         <v>112</v>
       </c>
@@ -7350,17 +7374,17 @@
       <c r="E3" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="F3" s="19">
-        <v>3965</v>
-      </c>
-      <c r="G3" s="19"/>
+      <c r="F3" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="G3" s="22"/>
       <c r="H3" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="I3" s="19">
-        <v>26126</v>
-      </c>
-      <c r="J3" s="19"/>
+      <c r="I3" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="J3" s="22"/>
       <c r="K3" s="17" t="s">
         <v>119</v>
       </c>
@@ -7404,15 +7428,15 @@
       <c r="E4" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="F4" s="19">
-        <v>12222</v>
-      </c>
-      <c r="G4" s="19"/>
+      <c r="F4" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="G4" s="22"/>
       <c r="H4" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
       <c r="K4" s="17"/>
       <c r="L4" s="17" t="s">
         <v>120</v>
@@ -7456,11 +7480,11 @@
       <c r="E5" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
       <c r="H5" s="17"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
       <c r="K5" s="17"/>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
@@ -7499,11 +7523,11 @@
       <c r="E6" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
       <c r="H6" s="17"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
@@ -7542,15 +7566,15 @@
       <c r="E7" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="G7" s="19"/>
+      <c r="G7" s="22"/>
       <c r="H7" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
@@ -7587,15 +7611,15 @@
       <c r="E8" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="G8" s="19"/>
+      <c r="G8" s="22"/>
       <c r="H8" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
       <c r="K8" s="17"/>
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
@@ -7632,13 +7656,13 @@
       <c r="E9" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19" t="s">
+      <c r="F9" s="22"/>
+      <c r="G9" s="22" t="s">
         <v>242</v>
       </c>
       <c r="H9" s="17"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
       <c r="K9" s="17"/>
       <c r="L9" s="17" t="s">
         <v>239</v>
@@ -7683,11 +7707,11 @@
       <c r="E10" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
       <c r="H10" s="17"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
       <c r="K10" s="17"/>
       <c r="L10" s="17" t="s">
         <v>239</v>
@@ -7734,11 +7758,11 @@
       <c r="E11" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
       <c r="H11" s="17"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
       <c r="K11" s="17"/>
       <c r="L11" s="17" t="s">
         <v>239</v>
@@ -7783,11 +7807,11 @@
       <c r="E12" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
       <c r="H12" s="17"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
       <c r="K12" s="17"/>
       <c r="L12" s="17" t="s">
         <v>239</v>
@@ -7832,13 +7856,13 @@
       <c r="E13" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19" t="s">
+      <c r="F13" s="22"/>
+      <c r="G13" s="22" t="s">
         <v>243</v>
       </c>
       <c r="H13" s="17"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
       <c r="K13" s="17"/>
       <c r="L13" s="17" t="s">
         <v>239</v>
@@ -7883,11 +7907,11 @@
       <c r="E14" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
       <c r="H14" s="17"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
       <c r="K14" s="17"/>
       <c r="L14" s="17" t="s">
         <v>239</v>
@@ -7932,11 +7956,11 @@
       <c r="E15" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
       <c r="H15" s="17"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19" t="s">
+      <c r="I15" s="22"/>
+      <c r="J15" s="22" t="s">
         <v>254</v>
       </c>
       <c r="K15" s="17" t="s">
@@ -7985,13 +8009,13 @@
       <c r="E16" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
       <c r="H16" s="17"/>
-      <c r="I16" s="17" t="s">
+      <c r="I16" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="J16" s="19"/>
+      <c r="J16" s="22"/>
       <c r="K16" s="17"/>
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
@@ -8026,11 +8050,11 @@
       <c r="E17" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
       <c r="H17" s="17"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19" t="s">
+      <c r="I17" s="22"/>
+      <c r="J17" s="22" t="s">
         <v>238</v>
       </c>
       <c r="K17" s="17"/>
@@ -8057,11 +8081,11 @@
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
       <c r="H18" s="17"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
       <c r="K18" s="17"/>
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
@@ -8082,11 +8106,11 @@
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
       <c r="H19" s="17"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
@@ -8107,11 +8131,11 @@
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
       <c r="H20" s="17"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
       <c r="K20" s="17"/>
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
@@ -8132,11 +8156,11 @@
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
       <c r="H21" s="17"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
@@ -8157,11 +8181,11 @@
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
       <c r="H22" s="17"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
       <c r="K22" s="17"/>
       <c r="L22" s="17"/>
       <c r="M22" s="17"/>
@@ -8182,11 +8206,11 @@
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
       <c r="H23" s="17"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
       <c r="K23" s="17"/>
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
@@ -8207,11 +8231,11 @@
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
       <c r="E24" s="17"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
       <c r="H24" s="17"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
       <c r="K24" s="17"/>
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
@@ -8232,11 +8256,11 @@
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
       <c r="H25" s="17"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
@@ -8257,11 +8281,11 @@
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
       <c r="H26" s="17"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
       <c r="K26" s="17"/>
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
@@ -8282,11 +8306,11 @@
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
       <c r="H27" s="17"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
       <c r="K27" s="17"/>
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
@@ -8307,11 +8331,11 @@
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
       <c r="H28" s="17"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
       <c r="K28" s="17"/>
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
@@ -8332,11 +8356,11 @@
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
       <c r="H29" s="17"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
       <c r="K29" s="17"/>
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
@@ -8357,11 +8381,11 @@
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
       <c r="H30" s="17"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
       <c r="K30" s="17"/>
       <c r="L30" s="17"/>
       <c r="M30" s="17"/>
@@ -8382,11 +8406,11 @@
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
       <c r="H31" s="17"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
       <c r="K31" s="17"/>
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
@@ -8407,11 +8431,11 @@
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
       <c r="H32" s="17"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
       <c r="K32" s="17"/>
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
@@ -8432,11 +8456,11 @@
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
       <c r="H33" s="17"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="22"/>
       <c r="K33" s="17"/>
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
@@ -8457,11 +8481,11 @@
       <c r="C34" s="17"/>
       <c r="D34" s="17"/>
       <c r="E34" s="17"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
       <c r="H34" s="17"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
       <c r="K34" s="17"/>
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
@@ -8482,11 +8506,11 @@
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
       <c r="H35" s="17"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
       <c r="K35" s="17"/>
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
@@ -8507,11 +8531,11 @@
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>
       <c r="E36" s="17"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
       <c r="H36" s="17"/>
-      <c r="I36" s="19"/>
-      <c r="J36" s="19"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="22"/>
       <c r="K36" s="17"/>
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
@@ -8532,11 +8556,11 @@
       <c r="C37" s="17"/>
       <c r="D37" s="17"/>
       <c r="E37" s="17"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
       <c r="H37" s="17"/>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
       <c r="K37" s="17"/>
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
@@ -8557,11 +8581,11 @@
       <c r="C38" s="17"/>
       <c r="D38" s="17"/>
       <c r="E38" s="17"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
       <c r="H38" s="17"/>
-      <c r="I38" s="19"/>
-      <c r="J38" s="19"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
       <c r="K38" s="17"/>
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
@@ -8582,11 +8606,11 @@
       <c r="C39" s="17"/>
       <c r="D39" s="17"/>
       <c r="E39" s="17"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
       <c r="H39" s="17"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
       <c r="K39" s="17"/>
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
@@ -8607,11 +8631,11 @@
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
       <c r="E40" s="17"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="22"/>
       <c r="H40" s="17"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
+      <c r="I40" s="22"/>
+      <c r="J40" s="22"/>
       <c r="K40" s="17"/>
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
@@ -8632,11 +8656,11 @@
       <c r="C41" s="17"/>
       <c r="D41" s="17"/>
       <c r="E41" s="17"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
       <c r="H41" s="17"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
       <c r="K41" s="17"/>
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
@@ -8657,11 +8681,11 @@
       <c r="C42" s="17"/>
       <c r="D42" s="17"/>
       <c r="E42" s="17"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
       <c r="H42" s="17"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="22"/>
       <c r="K42" s="17"/>
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
@@ -8682,11 +8706,11 @@
       <c r="C43" s="17"/>
       <c r="D43" s="17"/>
       <c r="E43" s="17"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
       <c r="H43" s="17"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="19"/>
+      <c r="I43" s="22"/>
+      <c r="J43" s="22"/>
       <c r="K43" s="17"/>
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
@@ -8707,11 +8731,11 @@
       <c r="C44" s="17"/>
       <c r="D44" s="17"/>
       <c r="E44" s="17"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
       <c r="H44" s="17"/>
-      <c r="I44" s="19"/>
-      <c r="J44" s="19"/>
+      <c r="I44" s="22"/>
+      <c r="J44" s="22"/>
       <c r="K44" s="17"/>
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
@@ -8732,11 +8756,11 @@
       <c r="C45" s="17"/>
       <c r="D45" s="17"/>
       <c r="E45" s="17"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="22"/>
       <c r="H45" s="17"/>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19"/>
+      <c r="I45" s="22"/>
+      <c r="J45" s="22"/>
       <c r="K45" s="17"/>
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
@@ -8757,11 +8781,11 @@
       <c r="C46" s="17"/>
       <c r="D46" s="17"/>
       <c r="E46" s="17"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="22"/>
       <c r="H46" s="17"/>
-      <c r="I46" s="19"/>
-      <c r="J46" s="19"/>
+      <c r="I46" s="22"/>
+      <c r="J46" s="22"/>
       <c r="K46" s="17"/>
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
@@ -8782,11 +8806,11 @@
       <c r="C47" s="17"/>
       <c r="D47" s="17"/>
       <c r="E47" s="17"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="22"/>
       <c r="H47" s="17"/>
-      <c r="I47" s="19"/>
-      <c r="J47" s="19"/>
+      <c r="I47" s="22"/>
+      <c r="J47" s="22"/>
       <c r="K47" s="17"/>
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
@@ -8807,11 +8831,11 @@
       <c r="C48" s="17"/>
       <c r="D48" s="17"/>
       <c r="E48" s="17"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="22"/>
       <c r="H48" s="17"/>
-      <c r="I48" s="19"/>
-      <c r="J48" s="19"/>
+      <c r="I48" s="22"/>
+      <c r="J48" s="22"/>
       <c r="K48" s="17"/>
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
@@ -8832,11 +8856,11 @@
       <c r="C49" s="17"/>
       <c r="D49" s="17"/>
       <c r="E49" s="17"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="22"/>
       <c r="H49" s="17"/>
-      <c r="I49" s="19"/>
-      <c r="J49" s="19"/>
+      <c r="I49" s="22"/>
+      <c r="J49" s="22"/>
       <c r="K49" s="17"/>
       <c r="L49" s="17"/>
       <c r="M49" s="17"/>
@@ -8857,11 +8881,11 @@
       <c r="C50" s="17"/>
       <c r="D50" s="17"/>
       <c r="E50" s="17"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="19"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="22"/>
       <c r="H50" s="17"/>
-      <c r="I50" s="19"/>
-      <c r="J50" s="19"/>
+      <c r="I50" s="22"/>
+      <c r="J50" s="22"/>
       <c r="K50" s="17"/>
       <c r="L50" s="17"/>
       <c r="M50" s="17"/>
@@ -8882,11 +8906,11 @@
       <c r="C51" s="17"/>
       <c r="D51" s="17"/>
       <c r="E51" s="17"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="22"/>
       <c r="H51" s="17"/>
-      <c r="I51" s="19"/>
-      <c r="J51" s="19"/>
+      <c r="I51" s="22"/>
+      <c r="J51" s="22"/>
       <c r="K51" s="17"/>
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
@@ -8907,11 +8931,11 @@
       <c r="C52" s="17"/>
       <c r="D52" s="17"/>
       <c r="E52" s="17"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
       <c r="H52" s="17"/>
-      <c r="I52" s="19"/>
-      <c r="J52" s="19"/>
+      <c r="I52" s="22"/>
+      <c r="J52" s="22"/>
       <c r="K52" s="17"/>
       <c r="L52" s="17"/>
       <c r="M52" s="17"/>
@@ -8932,11 +8956,11 @@
       <c r="C53" s="17"/>
       <c r="D53" s="17"/>
       <c r="E53" s="17"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
       <c r="H53" s="17"/>
-      <c r="I53" s="19"/>
-      <c r="J53" s="19"/>
+      <c r="I53" s="22"/>
+      <c r="J53" s="22"/>
       <c r="K53" s="17"/>
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
@@ -8957,11 +8981,11 @@
       <c r="C54" s="17"/>
       <c r="D54" s="17"/>
       <c r="E54" s="17"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="19"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="22"/>
       <c r="H54" s="17"/>
-      <c r="I54" s="19"/>
-      <c r="J54" s="19"/>
+      <c r="I54" s="22"/>
+      <c r="J54" s="22"/>
       <c r="K54" s="17"/>
       <c r="L54" s="17"/>
       <c r="M54" s="17"/>
@@ -8982,11 +9006,11 @@
       <c r="C55" s="17"/>
       <c r="D55" s="17"/>
       <c r="E55" s="17"/>
-      <c r="F55" s="19"/>
-      <c r="G55" s="19"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
       <c r="H55" s="17"/>
-      <c r="I55" s="19"/>
-      <c r="J55" s="19"/>
+      <c r="I55" s="22"/>
+      <c r="J55" s="22"/>
       <c r="K55" s="17"/>
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
@@ -9007,11 +9031,11 @@
       <c r="C56" s="17"/>
       <c r="D56" s="17"/>
       <c r="E56" s="17"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="19"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="22"/>
       <c r="H56" s="17"/>
-      <c r="I56" s="19"/>
-      <c r="J56" s="19"/>
+      <c r="I56" s="22"/>
+      <c r="J56" s="22"/>
       <c r="K56" s="17"/>
       <c r="L56" s="17"/>
       <c r="M56" s="17"/>
@@ -9032,11 +9056,11 @@
       <c r="C57" s="17"/>
       <c r="D57" s="17"/>
       <c r="E57" s="17"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="19"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="22"/>
       <c r="H57" s="17"/>
-      <c r="I57" s="19"/>
-      <c r="J57" s="19"/>
+      <c r="I57" s="22"/>
+      <c r="J57" s="22"/>
       <c r="K57" s="17"/>
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
@@ -9057,11 +9081,11 @@
       <c r="C58" s="17"/>
       <c r="D58" s="17"/>
       <c r="E58" s="17"/>
-      <c r="F58" s="19"/>
-      <c r="G58" s="19"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
       <c r="H58" s="17"/>
-      <c r="I58" s="19"/>
-      <c r="J58" s="19"/>
+      <c r="I58" s="22"/>
+      <c r="J58" s="22"/>
       <c r="K58" s="17"/>
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
@@ -9082,11 +9106,11 @@
       <c r="C59" s="17"/>
       <c r="D59" s="17"/>
       <c r="E59" s="17"/>
-      <c r="F59" s="19"/>
-      <c r="G59" s="19"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="22"/>
       <c r="H59" s="17"/>
-      <c r="I59" s="19"/>
-      <c r="J59" s="19"/>
+      <c r="I59" s="22"/>
+      <c r="J59" s="22"/>
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
@@ -9107,11 +9131,11 @@
       <c r="C60" s="17"/>
       <c r="D60" s="17"/>
       <c r="E60" s="17"/>
-      <c r="F60" s="19"/>
-      <c r="G60" s="19"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="22"/>
       <c r="H60" s="17"/>
-      <c r="I60" s="19"/>
-      <c r="J60" s="19"/>
+      <c r="I60" s="22"/>
+      <c r="J60" s="22"/>
       <c r="K60" s="17"/>
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
@@ -9132,11 +9156,11 @@
       <c r="C61" s="17"/>
       <c r="D61" s="17"/>
       <c r="E61" s="17"/>
-      <c r="F61" s="19"/>
-      <c r="G61" s="19"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
       <c r="H61" s="17"/>
-      <c r="I61" s="19"/>
-      <c r="J61" s="19"/>
+      <c r="I61" s="22"/>
+      <c r="J61" s="22"/>
       <c r="K61" s="17"/>
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
@@ -9157,11 +9181,11 @@
       <c r="C62" s="17"/>
       <c r="D62" s="17"/>
       <c r="E62" s="17"/>
-      <c r="F62" s="19"/>
-      <c r="G62" s="19"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
       <c r="H62" s="17"/>
-      <c r="I62" s="19"/>
-      <c r="J62" s="19"/>
+      <c r="I62" s="22"/>
+      <c r="J62" s="22"/>
       <c r="K62" s="17"/>
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
@@ -9182,11 +9206,11 @@
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
       <c r="E63" s="17"/>
-      <c r="F63" s="19"/>
-      <c r="G63" s="19"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
       <c r="H63" s="17"/>
-      <c r="I63" s="19"/>
-      <c r="J63" s="19"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="22"/>
       <c r="K63" s="17"/>
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
@@ -9207,11 +9231,11 @@
       <c r="C64" s="17"/>
       <c r="D64" s="17"/>
       <c r="E64" s="17"/>
-      <c r="F64" s="19"/>
-      <c r="G64" s="19"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="22"/>
       <c r="H64" s="17"/>
-      <c r="I64" s="19"/>
-      <c r="J64" s="19"/>
+      <c r="I64" s="22"/>
+      <c r="J64" s="22"/>
       <c r="K64" s="17"/>
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
@@ -9232,11 +9256,11 @@
       <c r="C65" s="17"/>
       <c r="D65" s="17"/>
       <c r="E65" s="17"/>
-      <c r="F65" s="19"/>
-      <c r="G65" s="19"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="22"/>
       <c r="H65" s="17"/>
-      <c r="I65" s="19"/>
-      <c r="J65" s="19"/>
+      <c r="I65" s="22"/>
+      <c r="J65" s="22"/>
       <c r="K65" s="17"/>
       <c r="L65" s="17"/>
       <c r="M65" s="17"/>
@@ -9257,11 +9281,11 @@
       <c r="C66" s="17"/>
       <c r="D66" s="17"/>
       <c r="E66" s="17"/>
-      <c r="F66" s="19"/>
-      <c r="G66" s="19"/>
+      <c r="F66" s="22"/>
+      <c r="G66" s="22"/>
       <c r="H66" s="17"/>
-      <c r="I66" s="19"/>
-      <c r="J66" s="19"/>
+      <c r="I66" s="22"/>
+      <c r="J66" s="22"/>
       <c r="K66" s="17"/>
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
@@ -9282,11 +9306,11 @@
       <c r="C67" s="17"/>
       <c r="D67" s="17"/>
       <c r="E67" s="17"/>
-      <c r="F67" s="19"/>
-      <c r="G67" s="19"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
       <c r="H67" s="17"/>
-      <c r="I67" s="19"/>
-      <c r="J67" s="19"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="22"/>
       <c r="K67" s="17"/>
       <c r="L67" s="17"/>
       <c r="M67" s="17"/>
@@ -9307,11 +9331,11 @@
       <c r="C68" s="17"/>
       <c r="D68" s="17"/>
       <c r="E68" s="17"/>
-      <c r="F68" s="19"/>
-      <c r="G68" s="19"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
       <c r="H68" s="17"/>
-      <c r="I68" s="19"/>
-      <c r="J68" s="19"/>
+      <c r="I68" s="22"/>
+      <c r="J68" s="22"/>
       <c r="K68" s="17"/>
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
@@ -9332,11 +9356,11 @@
       <c r="C69" s="17"/>
       <c r="D69" s="17"/>
       <c r="E69" s="17"/>
-      <c r="F69" s="19"/>
-      <c r="G69" s="19"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
       <c r="H69" s="17"/>
-      <c r="I69" s="19"/>
-      <c r="J69" s="19"/>
+      <c r="I69" s="22"/>
+      <c r="J69" s="22"/>
       <c r="K69" s="17"/>
       <c r="L69" s="17"/>
       <c r="M69" s="17"/>
@@ -9357,11 +9381,11 @@
       <c r="C70" s="17"/>
       <c r="D70" s="17"/>
       <c r="E70" s="17"/>
-      <c r="F70" s="19"/>
-      <c r="G70" s="19"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
       <c r="H70" s="17"/>
-      <c r="I70" s="19"/>
-      <c r="J70" s="19"/>
+      <c r="I70" s="22"/>
+      <c r="J70" s="22"/>
       <c r="K70" s="17"/>
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
@@ -9382,11 +9406,11 @@
       <c r="C71" s="17"/>
       <c r="D71" s="17"/>
       <c r="E71" s="17"/>
-      <c r="F71" s="19"/>
-      <c r="G71" s="19"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
       <c r="H71" s="17"/>
-      <c r="I71" s="19"/>
-      <c r="J71" s="19"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="22"/>
       <c r="K71" s="17"/>
       <c r="L71" s="17"/>
       <c r="M71" s="17"/>
@@ -9407,11 +9431,11 @@
       <c r="C72" s="17"/>
       <c r="D72" s="17"/>
       <c r="E72" s="17"/>
-      <c r="F72" s="19"/>
-      <c r="G72" s="19"/>
+      <c r="F72" s="22"/>
+      <c r="G72" s="22"/>
       <c r="H72" s="17"/>
-      <c r="I72" s="19"/>
-      <c r="J72" s="19"/>
+      <c r="I72" s="22"/>
+      <c r="J72" s="22"/>
       <c r="K72" s="17"/>
       <c r="L72" s="17"/>
       <c r="M72" s="17"/>
@@ -9432,11 +9456,11 @@
       <c r="C73" s="17"/>
       <c r="D73" s="17"/>
       <c r="E73" s="17"/>
-      <c r="F73" s="19"/>
-      <c r="G73" s="19"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
       <c r="H73" s="17"/>
-      <c r="I73" s="19"/>
-      <c r="J73" s="19"/>
+      <c r="I73" s="22"/>
+      <c r="J73" s="22"/>
       <c r="K73" s="17"/>
       <c r="L73" s="17"/>
       <c r="M73" s="17"/>
@@ -9457,11 +9481,11 @@
       <c r="C74" s="17"/>
       <c r="D74" s="17"/>
       <c r="E74" s="17"/>
-      <c r="F74" s="19"/>
-      <c r="G74" s="19"/>
+      <c r="F74" s="22"/>
+      <c r="G74" s="22"/>
       <c r="H74" s="17"/>
-      <c r="I74" s="19"/>
-      <c r="J74" s="19"/>
+      <c r="I74" s="22"/>
+      <c r="J74" s="22"/>
       <c r="K74" s="17"/>
       <c r="L74" s="17"/>
       <c r="M74" s="17"/>
@@ -9482,11 +9506,11 @@
       <c r="C75" s="17"/>
       <c r="D75" s="17"/>
       <c r="E75" s="17"/>
-      <c r="F75" s="19"/>
-      <c r="G75" s="19"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
       <c r="H75" s="17"/>
-      <c r="I75" s="19"/>
-      <c r="J75" s="19"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="22"/>
       <c r="K75" s="17"/>
       <c r="L75" s="17"/>
       <c r="M75" s="17"/>
@@ -9507,11 +9531,11 @@
       <c r="C76" s="17"/>
       <c r="D76" s="17"/>
       <c r="E76" s="17"/>
-      <c r="F76" s="19"/>
-      <c r="G76" s="19"/>
+      <c r="F76" s="22"/>
+      <c r="G76" s="22"/>
       <c r="H76" s="17"/>
-      <c r="I76" s="19"/>
-      <c r="J76" s="19"/>
+      <c r="I76" s="22"/>
+      <c r="J76" s="22"/>
       <c r="K76" s="17"/>
       <c r="L76" s="17"/>
       <c r="M76" s="17"/>
@@ -9532,11 +9556,11 @@
       <c r="C77" s="17"/>
       <c r="D77" s="17"/>
       <c r="E77" s="17"/>
-      <c r="F77" s="19"/>
-      <c r="G77" s="19"/>
+      <c r="F77" s="22"/>
+      <c r="G77" s="22"/>
       <c r="H77" s="17"/>
-      <c r="I77" s="19"/>
-      <c r="J77" s="19"/>
+      <c r="I77" s="22"/>
+      <c r="J77" s="22"/>
       <c r="K77" s="17"/>
       <c r="L77" s="17"/>
       <c r="M77" s="17"/>
@@ -9557,11 +9581,11 @@
       <c r="C78" s="17"/>
       <c r="D78" s="17"/>
       <c r="E78" s="17"/>
-      <c r="F78" s="19"/>
-      <c r="G78" s="19"/>
+      <c r="F78" s="22"/>
+      <c r="G78" s="22"/>
       <c r="H78" s="17"/>
-      <c r="I78" s="19"/>
-      <c r="J78" s="19"/>
+      <c r="I78" s="22"/>
+      <c r="J78" s="22"/>
       <c r="K78" s="17"/>
       <c r="L78" s="17"/>
       <c r="M78" s="17"/>
@@ -9582,11 +9606,11 @@
       <c r="C79" s="17"/>
       <c r="D79" s="17"/>
       <c r="E79" s="17"/>
-      <c r="F79" s="19"/>
-      <c r="G79" s="19"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
       <c r="H79" s="17"/>
-      <c r="I79" s="19"/>
-      <c r="J79" s="19"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="22"/>
       <c r="K79" s="17"/>
       <c r="L79" s="17"/>
       <c r="M79" s="17"/>
@@ -9607,11 +9631,11 @@
       <c r="C80" s="17"/>
       <c r="D80" s="17"/>
       <c r="E80" s="17"/>
-      <c r="F80" s="19"/>
-      <c r="G80" s="19"/>
+      <c r="F80" s="22"/>
+      <c r="G80" s="22"/>
       <c r="H80" s="17"/>
-      <c r="I80" s="19"/>
-      <c r="J80" s="19"/>
+      <c r="I80" s="22"/>
+      <c r="J80" s="22"/>
       <c r="K80" s="17"/>
       <c r="L80" s="17"/>
       <c r="M80" s="17"/>
@@ -9632,11 +9656,11 @@
       <c r="C81" s="17"/>
       <c r="D81" s="17"/>
       <c r="E81" s="17"/>
-      <c r="F81" s="19"/>
-      <c r="G81" s="19"/>
+      <c r="F81" s="22"/>
+      <c r="G81" s="22"/>
       <c r="H81" s="17"/>
-      <c r="I81" s="19"/>
-      <c r="J81" s="19"/>
+      <c r="I81" s="22"/>
+      <c r="J81" s="22"/>
       <c r="K81" s="17"/>
       <c r="L81" s="17"/>
       <c r="M81" s="17"/>
@@ -9657,11 +9681,11 @@
       <c r="C82" s="17"/>
       <c r="D82" s="17"/>
       <c r="E82" s="17"/>
-      <c r="F82" s="19"/>
-      <c r="G82" s="19"/>
+      <c r="F82" s="22"/>
+      <c r="G82" s="22"/>
       <c r="H82" s="17"/>
-      <c r="I82" s="19"/>
-      <c r="J82" s="19"/>
+      <c r="I82" s="22"/>
+      <c r="J82" s="22"/>
       <c r="K82" s="17"/>
       <c r="L82" s="17"/>
       <c r="M82" s="17"/>
@@ -9682,11 +9706,11 @@
       <c r="C83" s="17"/>
       <c r="D83" s="17"/>
       <c r="E83" s="17"/>
-      <c r="F83" s="19"/>
-      <c r="G83" s="19"/>
+      <c r="F83" s="22"/>
+      <c r="G83" s="22"/>
       <c r="H83" s="17"/>
-      <c r="I83" s="19"/>
-      <c r="J83" s="19"/>
+      <c r="I83" s="22"/>
+      <c r="J83" s="22"/>
       <c r="K83" s="17"/>
       <c r="L83" s="17"/>
       <c r="M83" s="17"/>
@@ -9707,11 +9731,11 @@
       <c r="C84" s="17"/>
       <c r="D84" s="17"/>
       <c r="E84" s="17"/>
-      <c r="F84" s="19"/>
-      <c r="G84" s="19"/>
+      <c r="F84" s="22"/>
+      <c r="G84" s="22"/>
       <c r="H84" s="17"/>
-      <c r="I84" s="19"/>
-      <c r="J84" s="19"/>
+      <c r="I84" s="22"/>
+      <c r="J84" s="22"/>
       <c r="K84" s="17"/>
       <c r="L84" s="17"/>
       <c r="M84" s="17"/>
@@ -9732,11 +9756,11 @@
       <c r="C85" s="17"/>
       <c r="D85" s="17"/>
       <c r="E85" s="17"/>
-      <c r="F85" s="19"/>
-      <c r="G85" s="19"/>
+      <c r="F85" s="22"/>
+      <c r="G85" s="22"/>
       <c r="H85" s="17"/>
-      <c r="I85" s="19"/>
-      <c r="J85" s="19"/>
+      <c r="I85" s="22"/>
+      <c r="J85" s="22"/>
       <c r="K85" s="17"/>
       <c r="L85" s="17"/>
       <c r="M85" s="17"/>
@@ -9757,11 +9781,11 @@
       <c r="C86" s="17"/>
       <c r="D86" s="17"/>
       <c r="E86" s="17"/>
-      <c r="F86" s="19"/>
-      <c r="G86" s="19"/>
+      <c r="F86" s="22"/>
+      <c r="G86" s="22"/>
       <c r="H86" s="17"/>
-      <c r="I86" s="19"/>
-      <c r="J86" s="19"/>
+      <c r="I86" s="22"/>
+      <c r="J86" s="22"/>
       <c r="K86" s="17"/>
       <c r="L86" s="17"/>
       <c r="M86" s="17"/>
@@ -9782,11 +9806,11 @@
       <c r="C87" s="17"/>
       <c r="D87" s="17"/>
       <c r="E87" s="17"/>
-      <c r="F87" s="19"/>
-      <c r="G87" s="19"/>
+      <c r="F87" s="22"/>
+      <c r="G87" s="22"/>
       <c r="H87" s="17"/>
-      <c r="I87" s="19"/>
-      <c r="J87" s="19"/>
+      <c r="I87" s="22"/>
+      <c r="J87" s="22"/>
       <c r="K87" s="17"/>
       <c r="L87" s="17"/>
       <c r="M87" s="17"/>
@@ -9807,11 +9831,11 @@
       <c r="C88" s="17"/>
       <c r="D88" s="17"/>
       <c r="E88" s="17"/>
-      <c r="F88" s="19"/>
-      <c r="G88" s="19"/>
+      <c r="F88" s="22"/>
+      <c r="G88" s="22"/>
       <c r="H88" s="17"/>
-      <c r="I88" s="19"/>
-      <c r="J88" s="19"/>
+      <c r="I88" s="22"/>
+      <c r="J88" s="22"/>
       <c r="K88" s="17"/>
       <c r="L88" s="17"/>
       <c r="M88" s="17"/>
@@ -9832,11 +9856,11 @@
       <c r="C89" s="17"/>
       <c r="D89" s="17"/>
       <c r="E89" s="17"/>
-      <c r="F89" s="19"/>
-      <c r="G89" s="19"/>
+      <c r="F89" s="22"/>
+      <c r="G89" s="22"/>
       <c r="H89" s="17"/>
-      <c r="I89" s="19"/>
-      <c r="J89" s="19"/>
+      <c r="I89" s="22"/>
+      <c r="J89" s="22"/>
       <c r="K89" s="17"/>
       <c r="L89" s="17"/>
       <c r="M89" s="17"/>
@@ -9857,11 +9881,11 @@
       <c r="C90" s="17"/>
       <c r="D90" s="17"/>
       <c r="E90" s="17"/>
-      <c r="F90" s="19"/>
-      <c r="G90" s="19"/>
+      <c r="F90" s="22"/>
+      <c r="G90" s="22"/>
       <c r="H90" s="17"/>
-      <c r="I90" s="19"/>
-      <c r="J90" s="19"/>
+      <c r="I90" s="22"/>
+      <c r="J90" s="22"/>
       <c r="K90" s="17"/>
       <c r="L90" s="17"/>
       <c r="M90" s="17"/>
@@ -9882,11 +9906,11 @@
       <c r="C91" s="17"/>
       <c r="D91" s="17"/>
       <c r="E91" s="17"/>
-      <c r="F91" s="19"/>
-      <c r="G91" s="19"/>
+      <c r="F91" s="22"/>
+      <c r="G91" s="22"/>
       <c r="H91" s="17"/>
-      <c r="I91" s="19"/>
-      <c r="J91" s="19"/>
+      <c r="I91" s="22"/>
+      <c r="J91" s="22"/>
       <c r="K91" s="17"/>
       <c r="L91" s="17"/>
       <c r="M91" s="17"/>
@@ -9907,11 +9931,11 @@
       <c r="C92" s="17"/>
       <c r="D92" s="17"/>
       <c r="E92" s="17"/>
-      <c r="F92" s="19"/>
-      <c r="G92" s="19"/>
+      <c r="F92" s="22"/>
+      <c r="G92" s="22"/>
       <c r="H92" s="17"/>
-      <c r="I92" s="19"/>
-      <c r="J92" s="19"/>
+      <c r="I92" s="22"/>
+      <c r="J92" s="22"/>
       <c r="K92" s="17"/>
       <c r="L92" s="17"/>
       <c r="M92" s="17"/>
@@ -9932,11 +9956,11 @@
       <c r="C93" s="17"/>
       <c r="D93" s="17"/>
       <c r="E93" s="17"/>
-      <c r="F93" s="19"/>
-      <c r="G93" s="19"/>
+      <c r="F93" s="22"/>
+      <c r="G93" s="22"/>
       <c r="H93" s="17"/>
-      <c r="I93" s="19"/>
-      <c r="J93" s="19"/>
+      <c r="I93" s="22"/>
+      <c r="J93" s="22"/>
       <c r="K93" s="17"/>
       <c r="L93" s="17"/>
       <c r="M93" s="17"/>
@@ -9957,11 +9981,11 @@
       <c r="C94" s="17"/>
       <c r="D94" s="17"/>
       <c r="E94" s="17"/>
-      <c r="F94" s="19"/>
-      <c r="G94" s="19"/>
+      <c r="F94" s="22"/>
+      <c r="G94" s="22"/>
       <c r="H94" s="17"/>
-      <c r="I94" s="19"/>
-      <c r="J94" s="19"/>
+      <c r="I94" s="22"/>
+      <c r="J94" s="22"/>
       <c r="K94" s="17"/>
       <c r="L94" s="17"/>
       <c r="M94" s="17"/>
@@ -9982,11 +10006,11 @@
       <c r="C95" s="17"/>
       <c r="D95" s="17"/>
       <c r="E95" s="17"/>
-      <c r="F95" s="19"/>
-      <c r="G95" s="19"/>
+      <c r="F95" s="22"/>
+      <c r="G95" s="22"/>
       <c r="H95" s="17"/>
-      <c r="I95" s="19"/>
-      <c r="J95" s="19"/>
+      <c r="I95" s="22"/>
+      <c r="J95" s="22"/>
       <c r="K95" s="17"/>
       <c r="L95" s="17"/>
       <c r="M95" s="17"/>
@@ -10007,11 +10031,11 @@
       <c r="C96" s="17"/>
       <c r="D96" s="17"/>
       <c r="E96" s="17"/>
-      <c r="F96" s="19"/>
-      <c r="G96" s="19"/>
+      <c r="F96" s="22"/>
+      <c r="G96" s="22"/>
       <c r="H96" s="17"/>
-      <c r="I96" s="19"/>
-      <c r="J96" s="19"/>
+      <c r="I96" s="22"/>
+      <c r="J96" s="22"/>
       <c r="K96" s="17"/>
       <c r="L96" s="17"/>
       <c r="M96" s="17"/>
@@ -10032,11 +10056,11 @@
       <c r="C97" s="17"/>
       <c r="D97" s="17"/>
       <c r="E97" s="17"/>
-      <c r="F97" s="19"/>
-      <c r="G97" s="19"/>
+      <c r="F97" s="22"/>
+      <c r="G97" s="22"/>
       <c r="H97" s="17"/>
-      <c r="I97" s="19"/>
-      <c r="J97" s="19"/>
+      <c r="I97" s="22"/>
+      <c r="J97" s="22"/>
       <c r="K97" s="17"/>
       <c r="L97" s="17"/>
       <c r="M97" s="17"/>
@@ -10057,11 +10081,11 @@
       <c r="C98" s="17"/>
       <c r="D98" s="17"/>
       <c r="E98" s="17"/>
-      <c r="F98" s="19"/>
-      <c r="G98" s="19"/>
+      <c r="F98" s="22"/>
+      <c r="G98" s="22"/>
       <c r="H98" s="17"/>
-      <c r="I98" s="19"/>
-      <c r="J98" s="19"/>
+      <c r="I98" s="22"/>
+      <c r="J98" s="22"/>
       <c r="K98" s="17"/>
       <c r="L98" s="17"/>
       <c r="M98" s="17"/>
@@ -10082,11 +10106,11 @@
       <c r="C99" s="17"/>
       <c r="D99" s="17"/>
       <c r="E99" s="17"/>
-      <c r="F99" s="19"/>
-      <c r="G99" s="19"/>
+      <c r="F99" s="22"/>
+      <c r="G99" s="22"/>
       <c r="H99" s="17"/>
-      <c r="I99" s="19"/>
-      <c r="J99" s="19"/>
+      <c r="I99" s="22"/>
+      <c r="J99" s="22"/>
       <c r="K99" s="17"/>
       <c r="L99" s="17"/>
       <c r="M99" s="17"/>
@@ -10107,11 +10131,11 @@
       <c r="C100" s="17"/>
       <c r="D100" s="17"/>
       <c r="E100" s="17"/>
-      <c r="F100" s="19"/>
-      <c r="G100" s="19"/>
+      <c r="F100" s="22"/>
+      <c r="G100" s="22"/>
       <c r="H100" s="17"/>
-      <c r="I100" s="19"/>
-      <c r="J100" s="19"/>
+      <c r="I100" s="22"/>
+      <c r="J100" s="22"/>
       <c r="K100" s="17"/>
       <c r="L100" s="17"/>
       <c r="M100" s="17"/>
@@ -10132,11 +10156,11 @@
       <c r="C101" s="17"/>
       <c r="D101" s="17"/>
       <c r="E101" s="17"/>
-      <c r="F101" s="19"/>
-      <c r="G101" s="19"/>
+      <c r="F101" s="22"/>
+      <c r="G101" s="22"/>
       <c r="H101" s="17"/>
-      <c r="I101" s="19"/>
-      <c r="J101" s="19"/>
+      <c r="I101" s="22"/>
+      <c r="J101" s="22"/>
       <c r="K101" s="17"/>
       <c r="L101" s="17"/>
       <c r="M101" s="17"/>
@@ -10157,11 +10181,11 @@
       <c r="C102" s="17"/>
       <c r="D102" s="17"/>
       <c r="E102" s="17"/>
-      <c r="F102" s="19"/>
-      <c r="G102" s="19"/>
+      <c r="F102" s="22"/>
+      <c r="G102" s="22"/>
       <c r="H102" s="17"/>
-      <c r="I102" s="19"/>
-      <c r="J102" s="19"/>
+      <c r="I102" s="22"/>
+      <c r="J102" s="22"/>
       <c r="K102" s="17"/>
       <c r="L102" s="17"/>
       <c r="M102" s="17"/>
@@ -10182,11 +10206,11 @@
       <c r="C103" s="17"/>
       <c r="D103" s="17"/>
       <c r="E103" s="17"/>
-      <c r="F103" s="19"/>
-      <c r="G103" s="19"/>
+      <c r="F103" s="22"/>
+      <c r="G103" s="22"/>
       <c r="H103" s="17"/>
-      <c r="I103" s="19"/>
-      <c r="J103" s="19"/>
+      <c r="I103" s="22"/>
+      <c r="J103" s="22"/>
       <c r="K103" s="17"/>
       <c r="L103" s="17"/>
       <c r="M103" s="17"/>
@@ -10207,11 +10231,11 @@
       <c r="C104" s="17"/>
       <c r="D104" s="17"/>
       <c r="E104" s="17"/>
-      <c r="F104" s="19"/>
-      <c r="G104" s="19"/>
+      <c r="F104" s="22"/>
+      <c r="G104" s="22"/>
       <c r="H104" s="17"/>
-      <c r="I104" s="19"/>
-      <c r="J104" s="19"/>
+      <c r="I104" s="22"/>
+      <c r="J104" s="22"/>
       <c r="K104" s="17"/>
       <c r="L104" s="17"/>
       <c r="M104" s="17"/>
@@ -10232,11 +10256,11 @@
       <c r="C105" s="17"/>
       <c r="D105" s="17"/>
       <c r="E105" s="17"/>
-      <c r="F105" s="19"/>
-      <c r="G105" s="19"/>
+      <c r="F105" s="22"/>
+      <c r="G105" s="22"/>
       <c r="H105" s="17"/>
-      <c r="I105" s="19"/>
-      <c r="J105" s="19"/>
+      <c r="I105" s="22"/>
+      <c r="J105" s="22"/>
       <c r="K105" s="17"/>
       <c r="L105" s="17"/>
       <c r="M105" s="17"/>
@@ -10257,11 +10281,11 @@
       <c r="C106" s="17"/>
       <c r="D106" s="17"/>
       <c r="E106" s="17"/>
-      <c r="F106" s="19"/>
-      <c r="G106" s="19"/>
+      <c r="F106" s="22"/>
+      <c r="G106" s="22"/>
       <c r="H106" s="17"/>
-      <c r="I106" s="19"/>
-      <c r="J106" s="19"/>
+      <c r="I106" s="22"/>
+      <c r="J106" s="22"/>
       <c r="K106" s="17"/>
       <c r="L106" s="17"/>
       <c r="M106" s="17"/>
@@ -10282,11 +10306,11 @@
       <c r="C107" s="17"/>
       <c r="D107" s="17"/>
       <c r="E107" s="17"/>
-      <c r="F107" s="19"/>
-      <c r="G107" s="19"/>
+      <c r="F107" s="22"/>
+      <c r="G107" s="22"/>
       <c r="H107" s="17"/>
-      <c r="I107" s="19"/>
-      <c r="J107" s="19"/>
+      <c r="I107" s="22"/>
+      <c r="J107" s="22"/>
       <c r="K107" s="17"/>
       <c r="L107" s="17"/>
       <c r="M107" s="17"/>
@@ -10307,11 +10331,11 @@
       <c r="C108" s="17"/>
       <c r="D108" s="17"/>
       <c r="E108" s="17"/>
-      <c r="F108" s="19"/>
-      <c r="G108" s="19"/>
+      <c r="F108" s="22"/>
+      <c r="G108" s="22"/>
       <c r="H108" s="17"/>
-      <c r="I108" s="19"/>
-      <c r="J108" s="19"/>
+      <c r="I108" s="22"/>
+      <c r="J108" s="22"/>
       <c r="K108" s="17"/>
       <c r="L108" s="17"/>
       <c r="M108" s="17"/>
@@ -10332,11 +10356,11 @@
       <c r="C109" s="17"/>
       <c r="D109" s="17"/>
       <c r="E109" s="17"/>
-      <c r="F109" s="19"/>
-      <c r="G109" s="19"/>
+      <c r="F109" s="22"/>
+      <c r="G109" s="22"/>
       <c r="H109" s="17"/>
-      <c r="I109" s="19"/>
-      <c r="J109" s="19"/>
+      <c r="I109" s="22"/>
+      <c r="J109" s="22"/>
       <c r="K109" s="17"/>
       <c r="L109" s="17"/>
       <c r="M109" s="17"/>
@@ -10357,11 +10381,11 @@
       <c r="C110" s="17"/>
       <c r="D110" s="17"/>
       <c r="E110" s="17"/>
-      <c r="F110" s="19"/>
-      <c r="G110" s="19"/>
+      <c r="F110" s="22"/>
+      <c r="G110" s="22"/>
       <c r="H110" s="17"/>
-      <c r="I110" s="19"/>
-      <c r="J110" s="19"/>
+      <c r="I110" s="22"/>
+      <c r="J110" s="22"/>
       <c r="K110" s="17"/>
       <c r="L110" s="17"/>
       <c r="M110" s="17"/>
@@ -10382,11 +10406,11 @@
       <c r="C111" s="17"/>
       <c r="D111" s="17"/>
       <c r="E111" s="17"/>
-      <c r="F111" s="19"/>
-      <c r="G111" s="19"/>
+      <c r="F111" s="22"/>
+      <c r="G111" s="22"/>
       <c r="H111" s="17"/>
-      <c r="I111" s="19"/>
-      <c r="J111" s="19"/>
+      <c r="I111" s="22"/>
+      <c r="J111" s="22"/>
       <c r="K111" s="17"/>
       <c r="L111" s="17"/>
       <c r="M111" s="17"/>
@@ -10407,11 +10431,11 @@
       <c r="C112" s="17"/>
       <c r="D112" s="17"/>
       <c r="E112" s="17"/>
-      <c r="F112" s="19"/>
-      <c r="G112" s="19"/>
+      <c r="F112" s="22"/>
+      <c r="G112" s="22"/>
       <c r="H112" s="17"/>
-      <c r="I112" s="19"/>
-      <c r="J112" s="19"/>
+      <c r="I112" s="22"/>
+      <c r="J112" s="22"/>
       <c r="K112" s="17"/>
       <c r="L112" s="17"/>
       <c r="M112" s="17"/>
@@ -10432,11 +10456,11 @@
       <c r="C113" s="17"/>
       <c r="D113" s="17"/>
       <c r="E113" s="17"/>
-      <c r="F113" s="19"/>
-      <c r="G113" s="19"/>
+      <c r="F113" s="22"/>
+      <c r="G113" s="22"/>
       <c r="H113" s="17"/>
-      <c r="I113" s="19"/>
-      <c r="J113" s="19"/>
+      <c r="I113" s="22"/>
+      <c r="J113" s="22"/>
       <c r="K113" s="17"/>
       <c r="L113" s="17"/>
       <c r="M113" s="17"/>
@@ -10457,11 +10481,11 @@
       <c r="C114" s="17"/>
       <c r="D114" s="17"/>
       <c r="E114" s="17"/>
-      <c r="F114" s="19"/>
-      <c r="G114" s="19"/>
+      <c r="F114" s="22"/>
+      <c r="G114" s="22"/>
       <c r="H114" s="17"/>
-      <c r="I114" s="19"/>
-      <c r="J114" s="19"/>
+      <c r="I114" s="22"/>
+      <c r="J114" s="22"/>
       <c r="K114" s="17"/>
       <c r="L114" s="17"/>
       <c r="M114" s="17"/>
@@ -10482,11 +10506,11 @@
       <c r="C115" s="17"/>
       <c r="D115" s="17"/>
       <c r="E115" s="17"/>
-      <c r="F115" s="19"/>
-      <c r="G115" s="19"/>
+      <c r="F115" s="22"/>
+      <c r="G115" s="22"/>
       <c r="H115" s="17"/>
-      <c r="I115" s="19"/>
-      <c r="J115" s="19"/>
+      <c r="I115" s="22"/>
+      <c r="J115" s="22"/>
       <c r="K115" s="17"/>
       <c r="L115" s="17"/>
       <c r="M115" s="17"/>
@@ -10507,11 +10531,11 @@
       <c r="C116" s="17"/>
       <c r="D116" s="17"/>
       <c r="E116" s="17"/>
-      <c r="F116" s="19"/>
-      <c r="G116" s="19"/>
+      <c r="F116" s="22"/>
+      <c r="G116" s="22"/>
       <c r="H116" s="17"/>
-      <c r="I116" s="19"/>
-      <c r="J116" s="19"/>
+      <c r="I116" s="22"/>
+      <c r="J116" s="22"/>
       <c r="K116" s="17"/>
       <c r="L116" s="17"/>
       <c r="M116" s="17"/>
@@ -10532,11 +10556,11 @@
       <c r="C117" s="17"/>
       <c r="D117" s="17"/>
       <c r="E117" s="17"/>
-      <c r="F117" s="19"/>
-      <c r="G117" s="19"/>
+      <c r="F117" s="22"/>
+      <c r="G117" s="22"/>
       <c r="H117" s="17"/>
-      <c r="I117" s="19"/>
-      <c r="J117" s="19"/>
+      <c r="I117" s="22"/>
+      <c r="J117" s="22"/>
       <c r="K117" s="17"/>
       <c r="L117" s="17"/>
       <c r="M117" s="17"/>
@@ -10557,11 +10581,11 @@
       <c r="C118" s="17"/>
       <c r="D118" s="17"/>
       <c r="E118" s="17"/>
-      <c r="F118" s="19"/>
-      <c r="G118" s="19"/>
+      <c r="F118" s="22"/>
+      <c r="G118" s="22"/>
       <c r="H118" s="17"/>
-      <c r="I118" s="19"/>
-      <c r="J118" s="19"/>
+      <c r="I118" s="22"/>
+      <c r="J118" s="22"/>
       <c r="K118" s="17"/>
       <c r="L118" s="17"/>
       <c r="M118" s="17"/>
@@ -10582,11 +10606,11 @@
       <c r="C119" s="17"/>
       <c r="D119" s="17"/>
       <c r="E119" s="17"/>
-      <c r="F119" s="19"/>
-      <c r="G119" s="19"/>
+      <c r="F119" s="22"/>
+      <c r="G119" s="22"/>
       <c r="H119" s="17"/>
-      <c r="I119" s="19"/>
-      <c r="J119" s="19"/>
+      <c r="I119" s="22"/>
+      <c r="J119" s="22"/>
       <c r="K119" s="17"/>
       <c r="L119" s="17"/>
       <c r="M119" s="17"/>
@@ -10607,11 +10631,11 @@
       <c r="C120" s="17"/>
       <c r="D120" s="17"/>
       <c r="E120" s="17"/>
-      <c r="F120" s="19"/>
-      <c r="G120" s="19"/>
+      <c r="F120" s="22"/>
+      <c r="G120" s="22"/>
       <c r="H120" s="17"/>
-      <c r="I120" s="19"/>
-      <c r="J120" s="19"/>
+      <c r="I120" s="22"/>
+      <c r="J120" s="22"/>
       <c r="K120" s="17"/>
       <c r="L120" s="17"/>
       <c r="M120" s="17"/>
@@ -10632,11 +10656,11 @@
       <c r="C121" s="17"/>
       <c r="D121" s="17"/>
       <c r="E121" s="17"/>
-      <c r="F121" s="19"/>
-      <c r="G121" s="19"/>
+      <c r="F121" s="22"/>
+      <c r="G121" s="22"/>
       <c r="H121" s="17"/>
-      <c r="I121" s="19"/>
-      <c r="J121" s="19"/>
+      <c r="I121" s="22"/>
+      <c r="J121" s="22"/>
       <c r="K121" s="17"/>
       <c r="L121" s="17"/>
       <c r="M121" s="17"/>
@@ -10657,11 +10681,11 @@
       <c r="C122" s="17"/>
       <c r="D122" s="17"/>
       <c r="E122" s="17"/>
-      <c r="F122" s="19"/>
-      <c r="G122" s="19"/>
+      <c r="F122" s="22"/>
+      <c r="G122" s="22"/>
       <c r="H122" s="17"/>
-      <c r="I122" s="19"/>
-      <c r="J122" s="19"/>
+      <c r="I122" s="22"/>
+      <c r="J122" s="22"/>
       <c r="K122" s="17"/>
       <c r="L122" s="17"/>
       <c r="M122" s="17"/>
@@ -10682,11 +10706,11 @@
       <c r="C123" s="17"/>
       <c r="D123" s="17"/>
       <c r="E123" s="17"/>
-      <c r="F123" s="19"/>
-      <c r="G123" s="19"/>
+      <c r="F123" s="22"/>
+      <c r="G123" s="22"/>
       <c r="H123" s="17"/>
-      <c r="I123" s="19"/>
-      <c r="J123" s="19"/>
+      <c r="I123" s="22"/>
+      <c r="J123" s="22"/>
       <c r="K123" s="17"/>
       <c r="L123" s="17"/>
       <c r="M123" s="17"/>
@@ -10707,11 +10731,11 @@
       <c r="C124" s="17"/>
       <c r="D124" s="17"/>
       <c r="E124" s="17"/>
-      <c r="F124" s="19"/>
-      <c r="G124" s="19"/>
+      <c r="F124" s="22"/>
+      <c r="G124" s="22"/>
       <c r="H124" s="17"/>
-      <c r="I124" s="19"/>
-      <c r="J124" s="19"/>
+      <c r="I124" s="22"/>
+      <c r="J124" s="22"/>
       <c r="K124" s="17"/>
       <c r="L124" s="17"/>
       <c r="M124" s="17"/>
@@ -10732,11 +10756,11 @@
       <c r="C125" s="17"/>
       <c r="D125" s="17"/>
       <c r="E125" s="17"/>
-      <c r="F125" s="19"/>
-      <c r="G125" s="19"/>
+      <c r="F125" s="22"/>
+      <c r="G125" s="22"/>
       <c r="H125" s="17"/>
-      <c r="I125" s="19"/>
-      <c r="J125" s="19"/>
+      <c r="I125" s="22"/>
+      <c r="J125" s="22"/>
       <c r="K125" s="17"/>
       <c r="L125" s="17"/>
       <c r="M125" s="17"/>
@@ -10757,11 +10781,11 @@
       <c r="C126" s="17"/>
       <c r="D126" s="17"/>
       <c r="E126" s="17"/>
-      <c r="F126" s="19"/>
-      <c r="G126" s="19"/>
+      <c r="F126" s="22"/>
+      <c r="G126" s="22"/>
       <c r="H126" s="17"/>
-      <c r="I126" s="19"/>
-      <c r="J126" s="19"/>
+      <c r="I126" s="22"/>
+      <c r="J126" s="22"/>
       <c r="K126" s="17"/>
       <c r="L126" s="17"/>
       <c r="M126" s="17"/>
@@ -10782,11 +10806,11 @@
       <c r="C127" s="17"/>
       <c r="D127" s="17"/>
       <c r="E127" s="17"/>
-      <c r="F127" s="19"/>
-      <c r="G127" s="19"/>
+      <c r="F127" s="22"/>
+      <c r="G127" s="22"/>
       <c r="H127" s="17"/>
-      <c r="I127" s="19"/>
-      <c r="J127" s="19"/>
+      <c r="I127" s="22"/>
+      <c r="J127" s="22"/>
       <c r="K127" s="17"/>
       <c r="L127" s="17"/>
       <c r="M127" s="17"/>
@@ -10807,11 +10831,11 @@
       <c r="C128" s="17"/>
       <c r="D128" s="17"/>
       <c r="E128" s="17"/>
-      <c r="F128" s="19"/>
-      <c r="G128" s="19"/>
+      <c r="F128" s="22"/>
+      <c r="G128" s="22"/>
       <c r="H128" s="17"/>
-      <c r="I128" s="19"/>
-      <c r="J128" s="19"/>
+      <c r="I128" s="22"/>
+      <c r="J128" s="22"/>
       <c r="K128" s="17"/>
       <c r="L128" s="17"/>
       <c r="M128" s="17"/>
@@ -10832,11 +10856,11 @@
       <c r="C129" s="17"/>
       <c r="D129" s="17"/>
       <c r="E129" s="17"/>
-      <c r="F129" s="19"/>
-      <c r="G129" s="19"/>
+      <c r="F129" s="22"/>
+      <c r="G129" s="22"/>
       <c r="H129" s="17"/>
-      <c r="I129" s="19"/>
-      <c r="J129" s="19"/>
+      <c r="I129" s="22"/>
+      <c r="J129" s="22"/>
       <c r="K129" s="17"/>
       <c r="L129" s="17"/>
       <c r="M129" s="17"/>
@@ -10857,11 +10881,11 @@
       <c r="C130" s="17"/>
       <c r="D130" s="17"/>
       <c r="E130" s="17"/>
-      <c r="F130" s="19"/>
-      <c r="G130" s="19"/>
+      <c r="F130" s="22"/>
+      <c r="G130" s="22"/>
       <c r="H130" s="17"/>
-      <c r="I130" s="19"/>
-      <c r="J130" s="19"/>
+      <c r="I130" s="22"/>
+      <c r="J130" s="22"/>
       <c r="K130" s="17"/>
       <c r="L130" s="17"/>
       <c r="M130" s="17"/>
@@ -10882,11 +10906,11 @@
       <c r="C131" s="17"/>
       <c r="D131" s="17"/>
       <c r="E131" s="17"/>
-      <c r="F131" s="19"/>
-      <c r="G131" s="19"/>
+      <c r="F131" s="22"/>
+      <c r="G131" s="22"/>
       <c r="H131" s="17"/>
-      <c r="I131" s="19"/>
-      <c r="J131" s="19"/>
+      <c r="I131" s="22"/>
+      <c r="J131" s="22"/>
       <c r="K131" s="17"/>
       <c r="L131" s="17"/>
       <c r="M131" s="17"/>
@@ -10907,11 +10931,11 @@
       <c r="C132" s="17"/>
       <c r="D132" s="17"/>
       <c r="E132" s="17"/>
-      <c r="F132" s="19"/>
-      <c r="G132" s="19"/>
+      <c r="F132" s="22"/>
+      <c r="G132" s="22"/>
       <c r="H132" s="17"/>
-      <c r="I132" s="19"/>
-      <c r="J132" s="19"/>
+      <c r="I132" s="22"/>
+      <c r="J132" s="22"/>
       <c r="K132" s="17"/>
       <c r="L132" s="17"/>
       <c r="M132" s="17"/>
@@ -10932,11 +10956,11 @@
       <c r="C133" s="17"/>
       <c r="D133" s="17"/>
       <c r="E133" s="17"/>
-      <c r="F133" s="19"/>
-      <c r="G133" s="19"/>
+      <c r="F133" s="22"/>
+      <c r="G133" s="22"/>
       <c r="H133" s="17"/>
-      <c r="I133" s="19"/>
-      <c r="J133" s="19"/>
+      <c r="I133" s="22"/>
+      <c r="J133" s="22"/>
       <c r="K133" s="17"/>
       <c r="L133" s="17"/>
       <c r="M133" s="17"/>
@@ -10957,11 +10981,11 @@
       <c r="C134" s="17"/>
       <c r="D134" s="17"/>
       <c r="E134" s="17"/>
-      <c r="F134" s="19"/>
-      <c r="G134" s="19"/>
+      <c r="F134" s="22"/>
+      <c r="G134" s="22"/>
       <c r="H134" s="17"/>
-      <c r="I134" s="19"/>
-      <c r="J134" s="19"/>
+      <c r="I134" s="22"/>
+      <c r="J134" s="22"/>
       <c r="K134" s="17"/>
       <c r="L134" s="17"/>
       <c r="M134" s="17"/>
@@ -10982,11 +11006,11 @@
       <c r="C135" s="17"/>
       <c r="D135" s="17"/>
       <c r="E135" s="17"/>
-      <c r="F135" s="19"/>
-      <c r="G135" s="19"/>
+      <c r="F135" s="22"/>
+      <c r="G135" s="22"/>
       <c r="H135" s="17"/>
-      <c r="I135" s="19"/>
-      <c r="J135" s="19"/>
+      <c r="I135" s="22"/>
+      <c r="J135" s="22"/>
       <c r="K135" s="17"/>
       <c r="L135" s="17"/>
       <c r="M135" s="17"/>
@@ -11007,11 +11031,11 @@
       <c r="C136" s="17"/>
       <c r="D136" s="17"/>
       <c r="E136" s="17"/>
-      <c r="F136" s="19"/>
-      <c r="G136" s="19"/>
+      <c r="F136" s="22"/>
+      <c r="G136" s="22"/>
       <c r="H136" s="17"/>
-      <c r="I136" s="19"/>
-      <c r="J136" s="19"/>
+      <c r="I136" s="22"/>
+      <c r="J136" s="22"/>
       <c r="K136" s="17"/>
       <c r="L136" s="17"/>
       <c r="M136" s="17"/>
@@ -11032,11 +11056,11 @@
       <c r="C137" s="17"/>
       <c r="D137" s="17"/>
       <c r="E137" s="17"/>
-      <c r="F137" s="19"/>
-      <c r="G137" s="19"/>
+      <c r="F137" s="22"/>
+      <c r="G137" s="22"/>
       <c r="H137" s="17"/>
-      <c r="I137" s="19"/>
-      <c r="J137" s="19"/>
+      <c r="I137" s="22"/>
+      <c r="J137" s="22"/>
       <c r="K137" s="17"/>
       <c r="L137" s="17"/>
       <c r="M137" s="17"/>
@@ -11057,11 +11081,11 @@
       <c r="C138" s="17"/>
       <c r="D138" s="17"/>
       <c r="E138" s="17"/>
-      <c r="F138" s="19"/>
-      <c r="G138" s="19"/>
+      <c r="F138" s="22"/>
+      <c r="G138" s="22"/>
       <c r="H138" s="17"/>
-      <c r="I138" s="19"/>
-      <c r="J138" s="19"/>
+      <c r="I138" s="22"/>
+      <c r="J138" s="22"/>
       <c r="K138" s="17"/>
       <c r="L138" s="17"/>
       <c r="M138" s="17"/>
@@ -11082,11 +11106,11 @@
       <c r="C139" s="17"/>
       <c r="D139" s="17"/>
       <c r="E139" s="17"/>
-      <c r="F139" s="19"/>
-      <c r="G139" s="19"/>
+      <c r="F139" s="22"/>
+      <c r="G139" s="22"/>
       <c r="H139" s="17"/>
-      <c r="I139" s="19"/>
-      <c r="J139" s="19"/>
+      <c r="I139" s="22"/>
+      <c r="J139" s="22"/>
       <c r="K139" s="17"/>
       <c r="L139" s="17"/>
       <c r="M139" s="17"/>
@@ -11107,11 +11131,11 @@
       <c r="C140" s="17"/>
       <c r="D140" s="17"/>
       <c r="E140" s="17"/>
-      <c r="F140" s="19"/>
-      <c r="G140" s="19"/>
+      <c r="F140" s="22"/>
+      <c r="G140" s="22"/>
       <c r="H140" s="17"/>
-      <c r="I140" s="19"/>
-      <c r="J140" s="19"/>
+      <c r="I140" s="22"/>
+      <c r="J140" s="22"/>
       <c r="K140" s="17"/>
       <c r="L140" s="17"/>
       <c r="M140" s="17"/>
@@ -11132,11 +11156,11 @@
       <c r="C141" s="17"/>
       <c r="D141" s="17"/>
       <c r="E141" s="17"/>
-      <c r="F141" s="19"/>
-      <c r="G141" s="19"/>
+      <c r="F141" s="22"/>
+      <c r="G141" s="22"/>
       <c r="H141" s="17"/>
-      <c r="I141" s="19"/>
-      <c r="J141" s="19"/>
+      <c r="I141" s="22"/>
+      <c r="J141" s="22"/>
       <c r="K141" s="17"/>
       <c r="L141" s="17"/>
       <c r="M141" s="17"/>
@@ -11157,11 +11181,11 @@
       <c r="C142" s="17"/>
       <c r="D142" s="17"/>
       <c r="E142" s="17"/>
-      <c r="F142" s="19"/>
-      <c r="G142" s="19"/>
+      <c r="F142" s="22"/>
+      <c r="G142" s="22"/>
       <c r="H142" s="17"/>
-      <c r="I142" s="19"/>
-      <c r="J142" s="19"/>
+      <c r="I142" s="22"/>
+      <c r="J142" s="22"/>
       <c r="K142" s="17"/>
       <c r="L142" s="17"/>
       <c r="M142" s="17"/>
@@ -11182,11 +11206,11 @@
       <c r="C143" s="17"/>
       <c r="D143" s="17"/>
       <c r="E143" s="17"/>
-      <c r="F143" s="19"/>
-      <c r="G143" s="19"/>
+      <c r="F143" s="22"/>
+      <c r="G143" s="22"/>
       <c r="H143" s="17"/>
-      <c r="I143" s="19"/>
-      <c r="J143" s="19"/>
+      <c r="I143" s="22"/>
+      <c r="J143" s="22"/>
       <c r="K143" s="17"/>
       <c r="L143" s="17"/>
       <c r="M143" s="17"/>
@@ -11207,11 +11231,11 @@
       <c r="C144" s="17"/>
       <c r="D144" s="17"/>
       <c r="E144" s="17"/>
-      <c r="F144" s="19"/>
-      <c r="G144" s="19"/>
+      <c r="F144" s="22"/>
+      <c r="G144" s="22"/>
       <c r="H144" s="17"/>
-      <c r="I144" s="19"/>
-      <c r="J144" s="19"/>
+      <c r="I144" s="22"/>
+      <c r="J144" s="22"/>
       <c r="K144" s="17"/>
       <c r="L144" s="17"/>
       <c r="M144" s="17"/>
@@ -11232,11 +11256,11 @@
       <c r="C145" s="17"/>
       <c r="D145" s="17"/>
       <c r="E145" s="17"/>
-      <c r="F145" s="19"/>
-      <c r="G145" s="19"/>
+      <c r="F145" s="22"/>
+      <c r="G145" s="22"/>
       <c r="H145" s="17"/>
-      <c r="I145" s="19"/>
-      <c r="J145" s="19"/>
+      <c r="I145" s="22"/>
+      <c r="J145" s="22"/>
       <c r="K145" s="17"/>
       <c r="L145" s="17"/>
       <c r="M145" s="17"/>
@@ -11257,11 +11281,11 @@
       <c r="C146" s="17"/>
       <c r="D146" s="17"/>
       <c r="E146" s="17"/>
-      <c r="F146" s="19"/>
-      <c r="G146" s="19"/>
+      <c r="F146" s="22"/>
+      <c r="G146" s="22"/>
       <c r="H146" s="17"/>
-      <c r="I146" s="19"/>
-      <c r="J146" s="19"/>
+      <c r="I146" s="22"/>
+      <c r="J146" s="22"/>
       <c r="K146" s="17"/>
       <c r="L146" s="17"/>
       <c r="M146" s="17"/>
@@ -11282,11 +11306,11 @@
       <c r="C147" s="17"/>
       <c r="D147" s="17"/>
       <c r="E147" s="17"/>
-      <c r="F147" s="19"/>
-      <c r="G147" s="19"/>
+      <c r="F147" s="22"/>
+      <c r="G147" s="22"/>
       <c r="H147" s="17"/>
-      <c r="I147" s="19"/>
-      <c r="J147" s="19"/>
+      <c r="I147" s="22"/>
+      <c r="J147" s="22"/>
       <c r="K147" s="17"/>
       <c r="L147" s="17"/>
       <c r="M147" s="17"/>
@@ -11307,11 +11331,11 @@
       <c r="C148" s="17"/>
       <c r="D148" s="17"/>
       <c r="E148" s="17"/>
-      <c r="F148" s="19"/>
-      <c r="G148" s="19"/>
+      <c r="F148" s="22"/>
+      <c r="G148" s="22"/>
       <c r="H148" s="17"/>
-      <c r="I148" s="19"/>
-      <c r="J148" s="19"/>
+      <c r="I148" s="22"/>
+      <c r="J148" s="22"/>
       <c r="K148" s="17"/>
       <c r="L148" s="17"/>
       <c r="M148" s="17"/>
@@ -11332,11 +11356,11 @@
       <c r="C149" s="17"/>
       <c r="D149" s="17"/>
       <c r="E149" s="17"/>
-      <c r="F149" s="19"/>
-      <c r="G149" s="19"/>
+      <c r="F149" s="22"/>
+      <c r="G149" s="22"/>
       <c r="H149" s="17"/>
-      <c r="I149" s="19"/>
-      <c r="J149" s="19"/>
+      <c r="I149" s="22"/>
+      <c r="J149" s="22"/>
       <c r="K149" s="17"/>
       <c r="L149" s="17"/>
       <c r="M149" s="17"/>
@@ -11357,11 +11381,11 @@
       <c r="C150" s="17"/>
       <c r="D150" s="17"/>
       <c r="E150" s="17"/>
-      <c r="F150" s="19"/>
-      <c r="G150" s="19"/>
+      <c r="F150" s="22"/>
+      <c r="G150" s="22"/>
       <c r="H150" s="17"/>
-      <c r="I150" s="19"/>
-      <c r="J150" s="19"/>
+      <c r="I150" s="22"/>
+      <c r="J150" s="22"/>
       <c r="K150" s="17"/>
       <c r="L150" s="17"/>
       <c r="M150" s="17"/>
@@ -11382,11 +11406,11 @@
       <c r="C151" s="17"/>
       <c r="D151" s="17"/>
       <c r="E151" s="17"/>
-      <c r="F151" s="19"/>
-      <c r="G151" s="19"/>
+      <c r="F151" s="22"/>
+      <c r="G151" s="22"/>
       <c r="H151" s="17"/>
-      <c r="I151" s="19"/>
-      <c r="J151" s="19"/>
+      <c r="I151" s="22"/>
+      <c r="J151" s="22"/>
       <c r="K151" s="17"/>
       <c r="L151" s="17"/>
       <c r="M151" s="17"/>
@@ -11407,11 +11431,11 @@
       <c r="C152" s="17"/>
       <c r="D152" s="17"/>
       <c r="E152" s="17"/>
-      <c r="F152" s="19"/>
-      <c r="G152" s="19"/>
+      <c r="F152" s="22"/>
+      <c r="G152" s="22"/>
       <c r="H152" s="17"/>
-      <c r="I152" s="19"/>
-      <c r="J152" s="19"/>
+      <c r="I152" s="22"/>
+      <c r="J152" s="22"/>
       <c r="K152" s="17"/>
       <c r="L152" s="17"/>
       <c r="M152" s="17"/>
@@ -11432,11 +11456,11 @@
       <c r="C153" s="17"/>
       <c r="D153" s="17"/>
       <c r="E153" s="17"/>
-      <c r="F153" s="19"/>
-      <c r="G153" s="19"/>
+      <c r="F153" s="22"/>
+      <c r="G153" s="22"/>
       <c r="H153" s="17"/>
-      <c r="I153" s="19"/>
-      <c r="J153" s="19"/>
+      <c r="I153" s="22"/>
+      <c r="J153" s="22"/>
       <c r="K153" s="17"/>
       <c r="L153" s="17"/>
       <c r="M153" s="17"/>
@@ -11457,11 +11481,11 @@
       <c r="C154" s="17"/>
       <c r="D154" s="17"/>
       <c r="E154" s="17"/>
-      <c r="F154" s="19"/>
-      <c r="G154" s="19"/>
+      <c r="F154" s="22"/>
+      <c r="G154" s="22"/>
       <c r="H154" s="17"/>
-      <c r="I154" s="19"/>
-      <c r="J154" s="19"/>
+      <c r="I154" s="22"/>
+      <c r="J154" s="22"/>
       <c r="K154" s="17"/>
       <c r="L154" s="17"/>
       <c r="M154" s="17"/>
@@ -11482,11 +11506,11 @@
       <c r="C155" s="17"/>
       <c r="D155" s="17"/>
       <c r="E155" s="17"/>
-      <c r="F155" s="19"/>
-      <c r="G155" s="19"/>
+      <c r="F155" s="22"/>
+      <c r="G155" s="22"/>
       <c r="H155" s="17"/>
-      <c r="I155" s="19"/>
-      <c r="J155" s="19"/>
+      <c r="I155" s="22"/>
+      <c r="J155" s="22"/>
       <c r="K155" s="17"/>
       <c r="L155" s="17"/>
       <c r="M155" s="17"/>
@@ -11507,11 +11531,11 @@
       <c r="C156" s="17"/>
       <c r="D156" s="17"/>
       <c r="E156" s="17"/>
-      <c r="F156" s="19"/>
-      <c r="G156" s="19"/>
+      <c r="F156" s="22"/>
+      <c r="G156" s="22"/>
       <c r="H156" s="17"/>
-      <c r="I156" s="19"/>
-      <c r="J156" s="19"/>
+      <c r="I156" s="22"/>
+      <c r="J156" s="22"/>
       <c r="K156" s="17"/>
       <c r="L156" s="17"/>
       <c r="M156" s="17"/>
@@ -11532,11 +11556,11 @@
       <c r="C157" s="17"/>
       <c r="D157" s="17"/>
       <c r="E157" s="17"/>
-      <c r="F157" s="19"/>
-      <c r="G157" s="19"/>
+      <c r="F157" s="22"/>
+      <c r="G157" s="22"/>
       <c r="H157" s="17"/>
-      <c r="I157" s="19"/>
-      <c r="J157" s="19"/>
+      <c r="I157" s="22"/>
+      <c r="J157" s="22"/>
       <c r="K157" s="17"/>
       <c r="L157" s="17"/>
       <c r="M157" s="17"/>
@@ -11557,11 +11581,11 @@
       <c r="C158" s="17"/>
       <c r="D158" s="17"/>
       <c r="E158" s="17"/>
-      <c r="F158" s="19"/>
-      <c r="G158" s="19"/>
+      <c r="F158" s="22"/>
+      <c r="G158" s="22"/>
       <c r="H158" s="17"/>
-      <c r="I158" s="19"/>
-      <c r="J158" s="19"/>
+      <c r="I158" s="22"/>
+      <c r="J158" s="22"/>
       <c r="K158" s="17"/>
       <c r="L158" s="17"/>
       <c r="M158" s="17"/>
@@ -11582,11 +11606,11 @@
       <c r="C159" s="17"/>
       <c r="D159" s="17"/>
       <c r="E159" s="17"/>
-      <c r="F159" s="19"/>
-      <c r="G159" s="19"/>
+      <c r="F159" s="22"/>
+      <c r="G159" s="22"/>
       <c r="H159" s="17"/>
-      <c r="I159" s="19"/>
-      <c r="J159" s="19"/>
+      <c r="I159" s="22"/>
+      <c r="J159" s="22"/>
       <c r="K159" s="17"/>
       <c r="L159" s="17"/>
       <c r="M159" s="17"/>
@@ -11607,11 +11631,11 @@
       <c r="C160" s="17"/>
       <c r="D160" s="17"/>
       <c r="E160" s="17"/>
-      <c r="F160" s="19"/>
-      <c r="G160" s="19"/>
+      <c r="F160" s="22"/>
+      <c r="G160" s="22"/>
       <c r="H160" s="17"/>
-      <c r="I160" s="19"/>
-      <c r="J160" s="19"/>
+      <c r="I160" s="22"/>
+      <c r="J160" s="22"/>
       <c r="K160" s="17"/>
       <c r="L160" s="17"/>
       <c r="M160" s="17"/>
@@ -11632,11 +11656,11 @@
       <c r="C161" s="17"/>
       <c r="D161" s="17"/>
       <c r="E161" s="17"/>
-      <c r="F161" s="19"/>
-      <c r="G161" s="19"/>
+      <c r="F161" s="22"/>
+      <c r="G161" s="22"/>
       <c r="H161" s="17"/>
-      <c r="I161" s="19"/>
-      <c r="J161" s="19"/>
+      <c r="I161" s="22"/>
+      <c r="J161" s="22"/>
       <c r="K161" s="17"/>
       <c r="L161" s="17"/>
       <c r="M161" s="17"/>
@@ -11657,11 +11681,11 @@
       <c r="C162" s="17"/>
       <c r="D162" s="17"/>
       <c r="E162" s="17"/>
-      <c r="F162" s="19"/>
-      <c r="G162" s="19"/>
+      <c r="F162" s="22"/>
+      <c r="G162" s="22"/>
       <c r="H162" s="17"/>
-      <c r="I162" s="19"/>
-      <c r="J162" s="19"/>
+      <c r="I162" s="22"/>
+      <c r="J162" s="22"/>
       <c r="K162" s="17"/>
       <c r="L162" s="17"/>
       <c r="M162" s="17"/>
@@ -11682,11 +11706,11 @@
       <c r="C163" s="17"/>
       <c r="D163" s="17"/>
       <c r="E163" s="17"/>
-      <c r="F163" s="19"/>
-      <c r="G163" s="19"/>
+      <c r="F163" s="22"/>
+      <c r="G163" s="22"/>
       <c r="H163" s="17"/>
-      <c r="I163" s="19"/>
-      <c r="J163" s="19"/>
+      <c r="I163" s="22"/>
+      <c r="J163" s="22"/>
       <c r="K163" s="17"/>
       <c r="L163" s="17"/>
       <c r="M163" s="17"/>
@@ -11707,11 +11731,11 @@
       <c r="C164" s="17"/>
       <c r="D164" s="17"/>
       <c r="E164" s="17"/>
-      <c r="F164" s="19"/>
-      <c r="G164" s="19"/>
+      <c r="F164" s="22"/>
+      <c r="G164" s="22"/>
       <c r="H164" s="17"/>
-      <c r="I164" s="19"/>
-      <c r="J164" s="19"/>
+      <c r="I164" s="22"/>
+      <c r="J164" s="22"/>
       <c r="K164" s="17"/>
       <c r="L164" s="17"/>
       <c r="M164" s="17"/>
@@ -11732,11 +11756,11 @@
       <c r="C165" s="17"/>
       <c r="D165" s="17"/>
       <c r="E165" s="17"/>
-      <c r="F165" s="19"/>
-      <c r="G165" s="19"/>
+      <c r="F165" s="22"/>
+      <c r="G165" s="22"/>
       <c r="H165" s="17"/>
-      <c r="I165" s="19"/>
-      <c r="J165" s="19"/>
+      <c r="I165" s="22"/>
+      <c r="J165" s="22"/>
       <c r="K165" s="17"/>
       <c r="L165" s="17"/>
       <c r="M165" s="17"/>
@@ -11757,11 +11781,11 @@
       <c r="C166" s="17"/>
       <c r="D166" s="17"/>
       <c r="E166" s="17"/>
-      <c r="F166" s="19"/>
-      <c r="G166" s="19"/>
+      <c r="F166" s="22"/>
+      <c r="G166" s="22"/>
       <c r="H166" s="17"/>
-      <c r="I166" s="19"/>
-      <c r="J166" s="19"/>
+      <c r="I166" s="22"/>
+      <c r="J166" s="22"/>
       <c r="K166" s="17"/>
       <c r="L166" s="17"/>
       <c r="M166" s="17"/>
@@ -11782,11 +11806,11 @@
       <c r="C167" s="17"/>
       <c r="D167" s="17"/>
       <c r="E167" s="17"/>
-      <c r="F167" s="19"/>
-      <c r="G167" s="19"/>
+      <c r="F167" s="22"/>
+      <c r="G167" s="22"/>
       <c r="H167" s="17"/>
-      <c r="I167" s="19"/>
-      <c r="J167" s="19"/>
+      <c r="I167" s="22"/>
+      <c r="J167" s="22"/>
       <c r="K167" s="17"/>
       <c r="L167" s="17"/>
       <c r="M167" s="17"/>
@@ -11807,11 +11831,11 @@
       <c r="C168" s="17"/>
       <c r="D168" s="17"/>
       <c r="E168" s="17"/>
-      <c r="F168" s="19"/>
-      <c r="G168" s="19"/>
+      <c r="F168" s="22"/>
+      <c r="G168" s="22"/>
       <c r="H168" s="17"/>
-      <c r="I168" s="19"/>
-      <c r="J168" s="19"/>
+      <c r="I168" s="22"/>
+      <c r="J168" s="22"/>
       <c r="K168" s="17"/>
       <c r="L168" s="17"/>
       <c r="M168" s="17"/>
@@ -11832,11 +11856,11 @@
       <c r="C169" s="17"/>
       <c r="D169" s="17"/>
       <c r="E169" s="17"/>
-      <c r="F169" s="19"/>
-      <c r="G169" s="19"/>
+      <c r="F169" s="22"/>
+      <c r="G169" s="22"/>
       <c r="H169" s="17"/>
-      <c r="I169" s="19"/>
-      <c r="J169" s="19"/>
+      <c r="I169" s="22"/>
+      <c r="J169" s="22"/>
       <c r="K169" s="17"/>
       <c r="L169" s="17"/>
       <c r="M169" s="17"/>
@@ -11857,11 +11881,11 @@
       <c r="C170" s="17"/>
       <c r="D170" s="17"/>
       <c r="E170" s="17"/>
-      <c r="F170" s="19"/>
-      <c r="G170" s="19"/>
+      <c r="F170" s="22"/>
+      <c r="G170" s="22"/>
       <c r="H170" s="17"/>
-      <c r="I170" s="19"/>
-      <c r="J170" s="19"/>
+      <c r="I170" s="22"/>
+      <c r="J170" s="22"/>
       <c r="K170" s="17"/>
       <c r="L170" s="17"/>
       <c r="M170" s="17"/>
@@ -11882,11 +11906,11 @@
       <c r="C171" s="17"/>
       <c r="D171" s="17"/>
       <c r="E171" s="17"/>
-      <c r="F171" s="19"/>
-      <c r="G171" s="19"/>
+      <c r="F171" s="22"/>
+      <c r="G171" s="22"/>
       <c r="H171" s="17"/>
-      <c r="I171" s="19"/>
-      <c r="J171" s="19"/>
+      <c r="I171" s="22"/>
+      <c r="J171" s="22"/>
       <c r="K171" s="17"/>
       <c r="L171" s="17"/>
       <c r="M171" s="17"/>
@@ -11907,11 +11931,11 @@
       <c r="C172" s="17"/>
       <c r="D172" s="17"/>
       <c r="E172" s="17"/>
-      <c r="F172" s="19"/>
-      <c r="G172" s="19"/>
+      <c r="F172" s="22"/>
+      <c r="G172" s="22"/>
       <c r="H172" s="17"/>
-      <c r="I172" s="19"/>
-      <c r="J172" s="19"/>
+      <c r="I172" s="22"/>
+      <c r="J172" s="22"/>
       <c r="K172" s="17"/>
       <c r="L172" s="17"/>
       <c r="M172" s="17"/>
@@ -11932,11 +11956,11 @@
       <c r="C173" s="17"/>
       <c r="D173" s="17"/>
       <c r="E173" s="17"/>
-      <c r="F173" s="19"/>
-      <c r="G173" s="19"/>
+      <c r="F173" s="22"/>
+      <c r="G173" s="22"/>
       <c r="H173" s="17"/>
-      <c r="I173" s="19"/>
-      <c r="J173" s="19"/>
+      <c r="I173" s="22"/>
+      <c r="J173" s="22"/>
       <c r="K173" s="17"/>
       <c r="L173" s="17"/>
       <c r="M173" s="17"/>
@@ -11957,11 +11981,11 @@
       <c r="C174" s="17"/>
       <c r="D174" s="17"/>
       <c r="E174" s="17"/>
-      <c r="F174" s="19"/>
-      <c r="G174" s="19"/>
+      <c r="F174" s="22"/>
+      <c r="G174" s="22"/>
       <c r="H174" s="17"/>
-      <c r="I174" s="19"/>
-      <c r="J174" s="19"/>
+      <c r="I174" s="22"/>
+      <c r="J174" s="22"/>
       <c r="K174" s="17"/>
       <c r="L174" s="17"/>
       <c r="M174" s="17"/>
@@ -11982,11 +12006,11 @@
       <c r="C175" s="17"/>
       <c r="D175" s="17"/>
       <c r="E175" s="17"/>
-      <c r="F175" s="19"/>
-      <c r="G175" s="19"/>
+      <c r="F175" s="22"/>
+      <c r="G175" s="22"/>
       <c r="H175" s="17"/>
-      <c r="I175" s="19"/>
-      <c r="J175" s="19"/>
+      <c r="I175" s="22"/>
+      <c r="J175" s="22"/>
       <c r="K175" s="17"/>
       <c r="L175" s="17"/>
       <c r="M175" s="17"/>
@@ -12007,11 +12031,11 @@
       <c r="C176" s="17"/>
       <c r="D176" s="17"/>
       <c r="E176" s="17"/>
-      <c r="F176" s="19"/>
-      <c r="G176" s="19"/>
+      <c r="F176" s="22"/>
+      <c r="G176" s="22"/>
       <c r="H176" s="17"/>
-      <c r="I176" s="19"/>
-      <c r="J176" s="19"/>
+      <c r="I176" s="22"/>
+      <c r="J176" s="22"/>
       <c r="K176" s="17"/>
       <c r="L176" s="17"/>
       <c r="M176" s="17"/>
@@ -12032,11 +12056,11 @@
       <c r="C177" s="17"/>
       <c r="D177" s="17"/>
       <c r="E177" s="17"/>
-      <c r="F177" s="19"/>
-      <c r="G177" s="19"/>
+      <c r="F177" s="22"/>
+      <c r="G177" s="22"/>
       <c r="H177" s="17"/>
-      <c r="I177" s="19"/>
-      <c r="J177" s="19"/>
+      <c r="I177" s="22"/>
+      <c r="J177" s="22"/>
       <c r="K177" s="17"/>
       <c r="L177" s="17"/>
       <c r="M177" s="17"/>
@@ -12057,11 +12081,11 @@
       <c r="C178" s="17"/>
       <c r="D178" s="17"/>
       <c r="E178" s="17"/>
-      <c r="F178" s="19"/>
-      <c r="G178" s="19"/>
+      <c r="F178" s="22"/>
+      <c r="G178" s="22"/>
       <c r="H178" s="17"/>
-      <c r="I178" s="19"/>
-      <c r="J178" s="19"/>
+      <c r="I178" s="22"/>
+      <c r="J178" s="22"/>
       <c r="K178" s="17"/>
       <c r="L178" s="17"/>
       <c r="M178" s="17"/>
@@ -12082,11 +12106,11 @@
       <c r="C179" s="17"/>
       <c r="D179" s="17"/>
       <c r="E179" s="17"/>
-      <c r="F179" s="19"/>
-      <c r="G179" s="19"/>
+      <c r="F179" s="22"/>
+      <c r="G179" s="22"/>
       <c r="H179" s="17"/>
-      <c r="I179" s="19"/>
-      <c r="J179" s="19"/>
+      <c r="I179" s="22"/>
+      <c r="J179" s="22"/>
       <c r="K179" s="17"/>
       <c r="L179" s="17"/>
       <c r="M179" s="17"/>
@@ -12107,11 +12131,11 @@
       <c r="C180" s="17"/>
       <c r="D180" s="17"/>
       <c r="E180" s="17"/>
-      <c r="F180" s="19"/>
-      <c r="G180" s="19"/>
+      <c r="F180" s="22"/>
+      <c r="G180" s="22"/>
       <c r="H180" s="17"/>
-      <c r="I180" s="19"/>
-      <c r="J180" s="19"/>
+      <c r="I180" s="22"/>
+      <c r="J180" s="22"/>
       <c r="K180" s="17"/>
       <c r="L180" s="17"/>
       <c r="M180" s="17"/>
@@ -12132,11 +12156,11 @@
       <c r="C181" s="17"/>
       <c r="D181" s="17"/>
       <c r="E181" s="17"/>
-      <c r="F181" s="19"/>
-      <c r="G181" s="19"/>
+      <c r="F181" s="22"/>
+      <c r="G181" s="22"/>
       <c r="H181" s="17"/>
-      <c r="I181" s="19"/>
-      <c r="J181" s="19"/>
+      <c r="I181" s="22"/>
+      <c r="J181" s="22"/>
       <c r="K181" s="17"/>
       <c r="L181" s="17"/>
       <c r="M181" s="17"/>
@@ -12157,11 +12181,11 @@
       <c r="C182" s="17"/>
       <c r="D182" s="17"/>
       <c r="E182" s="17"/>
-      <c r="F182" s="19"/>
-      <c r="G182" s="19"/>
+      <c r="F182" s="22"/>
+      <c r="G182" s="22"/>
       <c r="H182" s="17"/>
-      <c r="I182" s="19"/>
-      <c r="J182" s="19"/>
+      <c r="I182" s="22"/>
+      <c r="J182" s="22"/>
       <c r="K182" s="17"/>
       <c r="L182" s="17"/>
       <c r="M182" s="17"/>
@@ -12182,11 +12206,11 @@
       <c r="C183" s="17"/>
       <c r="D183" s="17"/>
       <c r="E183" s="17"/>
-      <c r="F183" s="19"/>
-      <c r="G183" s="19"/>
+      <c r="F183" s="22"/>
+      <c r="G183" s="22"/>
       <c r="H183" s="17"/>
-      <c r="I183" s="19"/>
-      <c r="J183" s="19"/>
+      <c r="I183" s="22"/>
+      <c r="J183" s="22"/>
       <c r="K183" s="17"/>
       <c r="L183" s="17"/>
       <c r="M183" s="17"/>
@@ -12207,11 +12231,11 @@
       <c r="C184" s="17"/>
       <c r="D184" s="17"/>
       <c r="E184" s="17"/>
-      <c r="F184" s="19"/>
-      <c r="G184" s="19"/>
+      <c r="F184" s="22"/>
+      <c r="G184" s="22"/>
       <c r="H184" s="17"/>
-      <c r="I184" s="19"/>
-      <c r="J184" s="19"/>
+      <c r="I184" s="22"/>
+      <c r="J184" s="22"/>
       <c r="K184" s="17"/>
       <c r="L184" s="17"/>
       <c r="M184" s="17"/>
@@ -12232,11 +12256,11 @@
       <c r="C185" s="17"/>
       <c r="D185" s="17"/>
       <c r="E185" s="17"/>
-      <c r="F185" s="19"/>
-      <c r="G185" s="19"/>
+      <c r="F185" s="22"/>
+      <c r="G185" s="22"/>
       <c r="H185" s="17"/>
-      <c r="I185" s="19"/>
-      <c r="J185" s="19"/>
+      <c r="I185" s="22"/>
+      <c r="J185" s="22"/>
       <c r="K185" s="17"/>
       <c r="L185" s="17"/>
       <c r="M185" s="17"/>
@@ -12257,11 +12281,11 @@
       <c r="C186" s="17"/>
       <c r="D186" s="17"/>
       <c r="E186" s="17"/>
-      <c r="F186" s="19"/>
-      <c r="G186" s="19"/>
+      <c r="F186" s="22"/>
+      <c r="G186" s="22"/>
       <c r="H186" s="17"/>
-      <c r="I186" s="19"/>
-      <c r="J186" s="19"/>
+      <c r="I186" s="22"/>
+      <c r="J186" s="22"/>
       <c r="K186" s="17"/>
       <c r="L186" s="17"/>
       <c r="M186" s="17"/>
@@ -12282,11 +12306,11 @@
       <c r="C187" s="17"/>
       <c r="D187" s="17"/>
       <c r="E187" s="17"/>
-      <c r="F187" s="19"/>
-      <c r="G187" s="19"/>
+      <c r="F187" s="22"/>
+      <c r="G187" s="22"/>
       <c r="H187" s="17"/>
-      <c r="I187" s="19"/>
-      <c r="J187" s="19"/>
+      <c r="I187" s="22"/>
+      <c r="J187" s="22"/>
       <c r="K187" s="17"/>
       <c r="L187" s="17"/>
       <c r="M187" s="17"/>
@@ -12307,11 +12331,11 @@
       <c r="C188" s="17"/>
       <c r="D188" s="17"/>
       <c r="E188" s="17"/>
-      <c r="F188" s="19"/>
-      <c r="G188" s="19"/>
+      <c r="F188" s="22"/>
+      <c r="G188" s="22"/>
       <c r="H188" s="17"/>
-      <c r="I188" s="19"/>
-      <c r="J188" s="19"/>
+      <c r="I188" s="22"/>
+      <c r="J188" s="22"/>
       <c r="K188" s="17"/>
       <c r="L188" s="17"/>
       <c r="M188" s="17"/>
@@ -12332,11 +12356,11 @@
       <c r="C189" s="17"/>
       <c r="D189" s="17"/>
       <c r="E189" s="17"/>
-      <c r="F189" s="19"/>
-      <c r="G189" s="19"/>
+      <c r="F189" s="22"/>
+      <c r="G189" s="22"/>
       <c r="H189" s="17"/>
-      <c r="I189" s="19"/>
-      <c r="J189" s="19"/>
+      <c r="I189" s="22"/>
+      <c r="J189" s="22"/>
       <c r="K189" s="17"/>
       <c r="L189" s="17"/>
       <c r="M189" s="17"/>
@@ -12357,11 +12381,11 @@
       <c r="C190" s="17"/>
       <c r="D190" s="17"/>
       <c r="E190" s="17"/>
-      <c r="F190" s="19"/>
-      <c r="G190" s="19"/>
+      <c r="F190" s="22"/>
+      <c r="G190" s="22"/>
       <c r="H190" s="17"/>
-      <c r="I190" s="19"/>
-      <c r="J190" s="19"/>
+      <c r="I190" s="22"/>
+      <c r="J190" s="22"/>
       <c r="K190" s="17"/>
       <c r="L190" s="17"/>
       <c r="M190" s="17"/>
@@ -12382,11 +12406,11 @@
       <c r="C191" s="17"/>
       <c r="D191" s="17"/>
       <c r="E191" s="17"/>
-      <c r="F191" s="19"/>
-      <c r="G191" s="19"/>
+      <c r="F191" s="22"/>
+      <c r="G191" s="22"/>
       <c r="H191" s="17"/>
-      <c r="I191" s="19"/>
-      <c r="J191" s="19"/>
+      <c r="I191" s="22"/>
+      <c r="J191" s="22"/>
       <c r="K191" s="17"/>
       <c r="L191" s="17"/>
       <c r="M191" s="17"/>
@@ -12407,11 +12431,11 @@
       <c r="C192" s="17"/>
       <c r="D192" s="17"/>
       <c r="E192" s="17"/>
-      <c r="F192" s="19"/>
-      <c r="G192" s="19"/>
+      <c r="F192" s="22"/>
+      <c r="G192" s="22"/>
       <c r="H192" s="17"/>
-      <c r="I192" s="19"/>
-      <c r="J192" s="19"/>
+      <c r="I192" s="22"/>
+      <c r="J192" s="22"/>
       <c r="K192" s="17"/>
       <c r="L192" s="17"/>
       <c r="M192" s="17"/>
@@ -12432,11 +12456,11 @@
       <c r="C193" s="17"/>
       <c r="D193" s="17"/>
       <c r="E193" s="17"/>
-      <c r="F193" s="19"/>
-      <c r="G193" s="19"/>
+      <c r="F193" s="22"/>
+      <c r="G193" s="22"/>
       <c r="H193" s="17"/>
-      <c r="I193" s="19"/>
-      <c r="J193" s="19"/>
+      <c r="I193" s="22"/>
+      <c r="J193" s="22"/>
       <c r="K193" s="17"/>
       <c r="L193" s="17"/>
       <c r="M193" s="17"/>
@@ -12457,11 +12481,11 @@
       <c r="C194" s="17"/>
       <c r="D194" s="17"/>
       <c r="E194" s="17"/>
-      <c r="F194" s="19"/>
-      <c r="G194" s="19"/>
+      <c r="F194" s="22"/>
+      <c r="G194" s="22"/>
       <c r="H194" s="17"/>
-      <c r="I194" s="19"/>
-      <c r="J194" s="19"/>
+      <c r="I194" s="22"/>
+      <c r="J194" s="22"/>
       <c r="K194" s="17"/>
       <c r="L194" s="17"/>
       <c r="M194" s="17"/>
@@ -12482,11 +12506,11 @@
       <c r="C195" s="17"/>
       <c r="D195" s="17"/>
       <c r="E195" s="17"/>
-      <c r="F195" s="19"/>
-      <c r="G195" s="19"/>
+      <c r="F195" s="22"/>
+      <c r="G195" s="22"/>
       <c r="H195" s="17"/>
-      <c r="I195" s="19"/>
-      <c r="J195" s="19"/>
+      <c r="I195" s="22"/>
+      <c r="J195" s="22"/>
       <c r="K195" s="17"/>
       <c r="L195" s="17"/>
       <c r="M195" s="17"/>
@@ -12507,11 +12531,11 @@
       <c r="C196" s="17"/>
       <c r="D196" s="17"/>
       <c r="E196" s="17"/>
-      <c r="F196" s="19"/>
-      <c r="G196" s="19"/>
+      <c r="F196" s="22"/>
+      <c r="G196" s="22"/>
       <c r="H196" s="17"/>
-      <c r="I196" s="19"/>
-      <c r="J196" s="19"/>
+      <c r="I196" s="22"/>
+      <c r="J196" s="22"/>
       <c r="K196" s="17"/>
       <c r="L196" s="17"/>
       <c r="M196" s="17"/>
@@ -12532,11 +12556,11 @@
       <c r="C197" s="17"/>
       <c r="D197" s="17"/>
       <c r="E197" s="17"/>
-      <c r="F197" s="19"/>
-      <c r="G197" s="19"/>
+      <c r="F197" s="22"/>
+      <c r="G197" s="22"/>
       <c r="H197" s="17"/>
-      <c r="I197" s="19"/>
-      <c r="J197" s="19"/>
+      <c r="I197" s="22"/>
+      <c r="J197" s="22"/>
       <c r="K197" s="17"/>
       <c r="L197" s="17"/>
       <c r="M197" s="17"/>
@@ -12557,11 +12581,11 @@
       <c r="C198" s="17"/>
       <c r="D198" s="17"/>
       <c r="E198" s="17"/>
-      <c r="F198" s="19"/>
-      <c r="G198" s="19"/>
+      <c r="F198" s="22"/>
+      <c r="G198" s="22"/>
       <c r="H198" s="17"/>
-      <c r="I198" s="19"/>
-      <c r="J198" s="19"/>
+      <c r="I198" s="22"/>
+      <c r="J198" s="22"/>
       <c r="K198" s="17"/>
       <c r="L198" s="17"/>
       <c r="M198" s="17"/>
@@ -12582,11 +12606,11 @@
       <c r="C199" s="17"/>
       <c r="D199" s="17"/>
       <c r="E199" s="17"/>
-      <c r="F199" s="19"/>
-      <c r="G199" s="19"/>
+      <c r="F199" s="22"/>
+      <c r="G199" s="22"/>
       <c r="H199" s="17"/>
-      <c r="I199" s="19"/>
-      <c r="J199" s="19"/>
+      <c r="I199" s="22"/>
+      <c r="J199" s="22"/>
       <c r="K199" s="17"/>
       <c r="L199" s="17"/>
       <c r="M199" s="17"/>
@@ -12607,11 +12631,11 @@
       <c r="C200" s="17"/>
       <c r="D200" s="17"/>
       <c r="E200" s="17"/>
-      <c r="F200" s="19"/>
-      <c r="G200" s="19"/>
+      <c r="F200" s="22"/>
+      <c r="G200" s="22"/>
       <c r="H200" s="17"/>
-      <c r="I200" s="19"/>
-      <c r="J200" s="19"/>
+      <c r="I200" s="22"/>
+      <c r="J200" s="22"/>
       <c r="K200" s="17"/>
       <c r="L200" s="17"/>
       <c r="M200" s="17"/>
@@ -12632,11 +12656,11 @@
       <c r="C201" s="17"/>
       <c r="D201" s="17"/>
       <c r="E201" s="17"/>
-      <c r="F201" s="19"/>
-      <c r="G201" s="19"/>
+      <c r="F201" s="22"/>
+      <c r="G201" s="22"/>
       <c r="H201" s="17"/>
-      <c r="I201" s="19"/>
-      <c r="J201" s="19"/>
+      <c r="I201" s="22"/>
+      <c r="J201" s="22"/>
       <c r="K201" s="17"/>
       <c r="L201" s="17"/>
       <c r="M201" s="17"/>
@@ -12657,11 +12681,11 @@
       <c r="C202" s="17"/>
       <c r="D202" s="17"/>
       <c r="E202" s="17"/>
-      <c r="F202" s="19"/>
-      <c r="G202" s="19"/>
+      <c r="F202" s="22"/>
+      <c r="G202" s="22"/>
       <c r="H202" s="17"/>
-      <c r="I202" s="19"/>
-      <c r="J202" s="19"/>
+      <c r="I202" s="22"/>
+      <c r="J202" s="22"/>
       <c r="K202" s="17"/>
       <c r="L202" s="17"/>
       <c r="M202" s="17"/>

--- a/data/Genealogie_MEME.xlsx
+++ b/data/Genealogie_MEME.xlsx
@@ -833,6 +833,21 @@
   <si>
     <t>14 juillet 1971</t>
   </si>
+  <si>
+    <t>https://drive.proton.me/urls/QK47AVTBE0#sYRXRYgNouVv</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/HWqtfSjG/notaire-enfant-parent-LAULAGNIER.png</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/QK47AVTBE0#sYRXRYgNouVv;https://i.postimg.cc/HWqtfSjG/notaire-enfant-parent-LAULAGNIER.png</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/QK47AVTBE0#sYRXRYgNouVv; https://i.postimg.cc/HWqtfSjG/notaire-enfant-parent-LAULAGNIER.png</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/gkvkD0fy/Photo-MEME.png</t>
+  </si>
 </sst>
 </file>
 
@@ -841,7 +856,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-40C]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -905,6 +920,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <color theme="10"/>
+      <u val="single"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -938,7 +970,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -988,6 +1020,12 @@
       <alignment wrapText="1" vertical="center" horizontal="center"/>
     </xf>
     <xf numFmtId="49" applyNumberFormat="1" fontId="7" applyFont="1" fillId="3" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="10" applyFont="1" fillId="3" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="3" applyFill="1" applyAlignment="1" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1390,7 +1428,7 @@
     <col width="16.90625" bestFit="1" customWidth="1" min="21" max="21"/>
     <col width="13.26953125" bestFit="1" customWidth="1" min="22" max="22"/>
     <col width="15.1796875" bestFit="1" customWidth="1" min="23" max="23"/>
-    <col width="13.36328125" bestFit="1" customWidth="1" min="24" max="24"/>
+    <col width="49.26953125" bestFit="1" customWidth="1" min="24" max="24"/>
     <col width="17.1796875" bestFit="1" customWidth="1" min="25" max="25"/>
     <col width="21.26953125" bestFit="1" customWidth="1" min="26" max="26"/>
   </cols>
@@ -1737,8 +1775,12 @@
       <c r="U6" s="2"/>
       <c r="V6" s="2"/>
       <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="2"/>
+      <c r="X6" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>273</v>
+      </c>
       <c r="Z6" s="2" t="s">
         <v>160</v>
       </c>
@@ -7228,8 +7270,8 @@
     <col width="16" customWidth="1" min="19" max="19" style="16"/>
     <col width="30" customWidth="1" min="20" max="20" style="16"/>
     <col width="34" customWidth="1" min="21" max="21" style="16"/>
-    <col width="34" customWidth="1" min="22" max="22" style="16"/>
-    <col width="40" customWidth="1" min="23" max="23" style="16"/>
+    <col width="76.6328125" customWidth="1" min="22" max="22" style="16" bestFit="1"/>
+    <col width="57.81640625" customWidth="1" min="23" max="23" style="16" bestFit="1"/>
     <col min="24" max="16384" width="8.7265625" style="16"/>
   </cols>
   <sheetData>
@@ -7359,6 +7401,9 @@
       <c r="T2" s="17"/>
       <c r="U2" s="17"/>
       <c r="V2" s="17"/>
+      <c r="W2" s="16" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="3" customFormat="1" s="16">
       <c r="A3" s="17" t="s">
@@ -7691,7 +7736,9 @@
       <c r="V9" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="W9" s="17"/>
+      <c r="W9" s="24" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="10" customFormat="1" s="16">
       <c r="A10" s="17" t="s">
@@ -7742,7 +7789,9 @@
       <c r="V10" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="W10" s="17"/>
+      <c r="W10" s="24" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="11" customFormat="1" s="16">
       <c r="A11" s="17" t="s">
@@ -7791,7 +7840,9 @@
       <c r="V11" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="W11" s="17"/>
+      <c r="W11" s="24" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="12" customFormat="1" s="16">
       <c r="A12" s="17" t="s">
@@ -7840,7 +7891,9 @@
       <c r="V12" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="W12" s="17"/>
+      <c r="W12" s="24" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="13" customFormat="1" s="16">
       <c r="A13" s="17" t="s">
@@ -7891,7 +7944,9 @@
       <c r="V13" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="W13" s="17"/>
+      <c r="W13" s="24" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="14" customFormat="1" s="16">
       <c r="A14" s="17" t="s">
@@ -7940,7 +7995,9 @@
       <c r="V14" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="W14" s="17"/>
+      <c r="W14" s="24" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="15" customFormat="1" s="16">
       <c r="A15" s="17" t="s">
@@ -7993,7 +8050,9 @@
       <c r="V15" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="W15" s="17"/>
+      <c r="W15" s="24" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="16" customFormat="1" s="16">
       <c r="A16" s="17" t="s">
@@ -8036,10 +8095,14 @@
       <c r="T16" s="17"/>
       <c r="U16" s="17"/>
       <c r="V16" s="17"/>
-      <c r="W16" s="17"/>
+      <c r="W16" s="24" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="17" customFormat="1" s="16">
-      <c r="A17" s="17"/>
+      <c r="A17" s="17" t="s">
+        <v>244</v>
+      </c>
       <c r="B17" s="17" t="s">
         <v>199</v>
       </c>
@@ -8068,12 +8131,18 @@
       <c r="Q17" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="R17" s="17"/>
-      <c r="S17" s="17"/>
+      <c r="R17" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="S17" s="17" t="s">
+        <v>210</v>
+      </c>
       <c r="T17" s="17"/>
       <c r="U17" s="17"/>
       <c r="V17" s="17"/>
-      <c r="W17" s="17"/>
+      <c r="W17" s="24" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="18" customFormat="1" s="16">
       <c r="A18" s="17"/>

--- a/data/Genealogie_MEME.xlsx
+++ b/data/Genealogie_MEME.xlsx
@@ -847,6 +847,15 @@
   </si>
   <si>
     <t>https://i.postimg.cc/gkvkD0fy/Photo-MEME.png</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/KjSVSDs0/homme-inconnu.png</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/MH242mr3/femme-inconnue.png</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/TPQYPpXc/Photo-PEPE.png</t>
   </si>
 </sst>
 </file>
@@ -7458,6 +7467,9 @@
       <c r="T3" s="17"/>
       <c r="U3" s="17"/>
       <c r="V3" s="17"/>
+      <c r="W3" s="16" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="4" customFormat="1" s="16">
       <c r="A4" s="17" t="s">
@@ -7509,6 +7521,9 @@
       <c r="U4" s="17"/>
       <c r="V4" s="17" t="s">
         <v>264</v>
+      </c>
+      <c r="W4" s="16" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="5" customFormat="1" s="16">
@@ -7550,7 +7565,9 @@
       <c r="T5" s="17"/>
       <c r="U5" s="17"/>
       <c r="V5" s="17"/>
-      <c r="W5" s="17"/>
+      <c r="W5" s="17" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="6" customFormat="1" s="16">
       <c r="A6" s="17" t="s">
@@ -7593,7 +7610,9 @@
       <c r="T6" s="17"/>
       <c r="U6" s="17"/>
       <c r="V6" s="17"/>
-      <c r="W6" s="17"/>
+      <c r="W6" s="17" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="7" customFormat="1" s="16">
       <c r="A7" s="17" t="s">
@@ -7640,7 +7659,9 @@
       <c r="T7" s="17"/>
       <c r="U7" s="17"/>
       <c r="V7" s="17"/>
-      <c r="W7" s="17"/>
+      <c r="W7" s="17" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="8" customFormat="1" s="16">
       <c r="A8" s="17" t="s">
@@ -7685,7 +7706,9 @@
       <c r="T8" s="17"/>
       <c r="U8" s="17"/>
       <c r="V8" s="17"/>
-      <c r="W8" s="17"/>
+      <c r="W8" s="17" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="9" customFormat="1" s="16">
       <c r="A9" s="17" t="s">
@@ -7737,7 +7760,7 @@
         <v>224</v>
       </c>
       <c r="W9" s="24" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" customFormat="1" s="16">
@@ -7790,7 +7813,7 @@
         <v>231</v>
       </c>
       <c r="W10" s="24" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" customFormat="1" s="16">
@@ -7841,7 +7864,7 @@
         <v>230</v>
       </c>
       <c r="W11" s="24" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" customFormat="1" s="16">
@@ -7892,7 +7915,7 @@
         <v>229</v>
       </c>
       <c r="W12" s="24" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" customFormat="1" s="16">
@@ -7945,7 +7968,7 @@
         <v>228</v>
       </c>
       <c r="W13" s="24" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" customFormat="1" s="16">
@@ -7996,7 +8019,7 @@
         <v>232</v>
       </c>
       <c r="W14" s="24" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" customFormat="1" s="16">
@@ -8051,7 +8074,7 @@
         <v>252</v>
       </c>
       <c r="W15" s="24" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" customFormat="1" s="16">
@@ -8096,7 +8119,7 @@
       <c r="U16" s="17"/>
       <c r="V16" s="17"/>
       <c r="W16" s="24" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" customFormat="1" s="16">
@@ -8141,7 +8164,7 @@
       <c r="U17" s="17"/>
       <c r="V17" s="17"/>
       <c r="W17" s="24" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" customFormat="1" s="16">

--- a/data/Genealogie_MEME.xlsx
+++ b/data/Genealogie_MEME.xlsx
@@ -856,6 +856,12 @@
   </si>
   <si>
     <t>https://i.postimg.cc/TPQYPpXc/Photo-PEPE.png</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/5tFdhyNh/femme-inconnue.png</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/k5t30GXk/homme-inconnu.png</t>
   </si>
 </sst>
 </file>
@@ -7523,7 +7529,7 @@
         <v>264</v>
       </c>
       <c r="W4" s="16" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" customFormat="1" s="16">
@@ -7566,7 +7572,7 @@
       <c r="U5" s="17"/>
       <c r="V5" s="17"/>
       <c r="W5" s="17" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" customFormat="1" s="16">
@@ -7611,7 +7617,7 @@
       <c r="U6" s="17"/>
       <c r="V6" s="17"/>
       <c r="W6" s="17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" customFormat="1" s="16">
@@ -7660,7 +7666,7 @@
       <c r="U7" s="17"/>
       <c r="V7" s="17"/>
       <c r="W7" s="17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" customFormat="1" s="16">
@@ -7707,7 +7713,7 @@
       <c r="U8" s="17"/>
       <c r="V8" s="17"/>
       <c r="W8" s="17" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" customFormat="1" s="16">
@@ -7760,7 +7766,7 @@
         <v>224</v>
       </c>
       <c r="W9" s="24" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" customFormat="1" s="16">
@@ -7813,7 +7819,7 @@
         <v>231</v>
       </c>
       <c r="W10" s="24" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" customFormat="1" s="16">
@@ -7864,7 +7870,7 @@
         <v>230</v>
       </c>
       <c r="W11" s="24" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" customFormat="1" s="16">
@@ -7915,7 +7921,7 @@
         <v>229</v>
       </c>
       <c r="W12" s="24" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13" customFormat="1" s="16">
@@ -7968,7 +7974,7 @@
         <v>228</v>
       </c>
       <c r="W13" s="24" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" customFormat="1" s="16">
@@ -8019,7 +8025,7 @@
         <v>232</v>
       </c>
       <c r="W14" s="24" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" customFormat="1" s="16">
@@ -8074,7 +8080,7 @@
         <v>252</v>
       </c>
       <c r="W15" s="24" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" customFormat="1" s="16">
@@ -8119,7 +8125,7 @@
       <c r="U16" s="17"/>
       <c r="V16" s="17"/>
       <c r="W16" s="24" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" customFormat="1" s="16">
@@ -8164,7 +8170,7 @@
       <c r="U17" s="17"/>
       <c r="V17" s="17"/>
       <c r="W17" s="24" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" customFormat="1" s="16">

--- a/data/Genealogie_MEME.xlsx
+++ b/data/Genealogie_MEME.xlsx
@@ -862,6 +862,12 @@
   </si>
   <si>
     <t>https://i.postimg.cc/k5t30GXk/homme-inconnu.png</t>
+  </si>
+  <si>
+    <t>PEPE</t>
+  </si>
+  <si>
+    <t>P03</t>
   </si>
 </sst>
 </file>
@@ -7286,7 +7292,7 @@
     <col width="30" customWidth="1" min="20" max="20" style="16"/>
     <col width="34" customWidth="1" min="21" max="21" style="16"/>
     <col width="76.6328125" customWidth="1" min="22" max="22" style="16" bestFit="1"/>
-    <col width="57.81640625" customWidth="1" min="23" max="23" style="16" bestFit="1"/>
+    <col width="43.26953125" customWidth="1" min="23" max="23" style="16" bestFit="1"/>
     <col min="24" max="16384" width="8.7265625" style="16"/>
   </cols>
   <sheetData>
@@ -7457,12 +7463,14 @@
       <c r="N3" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="O3" s="17"/>
+      <c r="O3" s="17" t="s">
+        <v>283</v>
+      </c>
       <c r="P3" s="17" t="s">
         <v>56</v>
       </c>
       <c r="Q3" s="17" t="s">
-        <v>152</v>
+        <v>282</v>
       </c>
       <c r="R3" s="17" t="s">
         <v>58</v>

--- a/data/Genealogie_MEME.xlsx
+++ b/data/Genealogie_MEME.xlsx
@@ -868,6 +868,93 @@
   </si>
   <si>
     <t>P03</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/HLsRkWmw/carte-de-priorite-des-meres-de-famille.png</t>
+  </si>
+  <si>
+    <t>P031</t>
+  </si>
+  <si>
+    <t>P032</t>
+  </si>
+  <si>
+    <t>?? 1914</t>
+  </si>
+  <si>
+    <t>P02;P031</t>
+  </si>
+  <si>
+    <t>P002;P031</t>
+  </si>
+  <si>
+    <t>P003;P002</t>
+  </si>
+  <si>
+    <t>D007</t>
+  </si>
+  <si>
+    <t>Carte de priorité des mère de famille</t>
+  </si>
+  <si>
+    <t>ioriginal</t>
+  </si>
+  <si>
+    <t>SNCF</t>
+  </si>
+  <si>
+    <t>BERTHOLON Elise</t>
+  </si>
+  <si>
+    <t>Mamie</t>
+  </si>
+  <si>
+    <t>Simone Petite Valise</t>
+  </si>
+  <si>
+    <t>Smone Grande Valise</t>
+  </si>
+  <si>
+    <t>https://drive.proton.me/urls/33YEJ7WG18#VB4EHFSB4IQM</t>
+  </si>
+  <si>
+    <t>Marius</t>
+  </si>
+  <si>
+    <t>16 octobre 1925</t>
+  </si>
+  <si>
+    <t>P003;P002;P031</t>
+  </si>
+  <si>
+    <t>P002;P031;P032</t>
+  </si>
+  <si>
+    <t>P003;P002;P032</t>
+  </si>
+  <si>
+    <t>P033</t>
+  </si>
+  <si>
+    <t>Alban Marius Laurens</t>
+  </si>
+  <si>
+    <t>3 juillet 1913</t>
+  </si>
+  <si>
+    <t>P003;P002;P031;P032</t>
+  </si>
+  <si>
+    <t>P003;P002;P031;P033</t>
+  </si>
+  <si>
+    <t>P003;P002;P032;P033</t>
+  </si>
+  <si>
+    <t>P002;P031;P032;P033</t>
+  </si>
+  <si>
+    <t>3 juillet 1913 (batisé)</t>
   </si>
 </sst>
 </file>
@@ -1430,7 +1517,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="11.6328125" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="23.6328125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="30.453125" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="13.81640625" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="11.36328125" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="26.36328125" bestFit="1" customWidth="1" min="5" max="5"/>
@@ -1583,7 +1670,7 @@
       <c r="X2" s="2"/>
       <c r="Y2" s="2"/>
       <c r="Z2" s="2" t="s">
-        <v>140</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3">
@@ -1632,10 +1719,12 @@
       </c>
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
+      <c r="X3" s="2" t="s">
+        <v>299</v>
+      </c>
       <c r="Y3" s="2"/>
       <c r="Z3" s="2" t="s">
-        <v>160</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4">
@@ -1691,7 +1780,7 @@
       <c r="X4" s="2"/>
       <c r="Y4" s="2"/>
       <c r="Z4" s="2" t="s">
-        <v>160</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5">
@@ -1745,7 +1834,7 @@
       <c r="X5" s="2"/>
       <c r="Y5" s="2"/>
       <c r="Z5" s="2" t="s">
-        <v>160</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6">
@@ -1803,7 +1892,7 @@
         <v>273</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>160</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7">
@@ -1850,16 +1939,30 @@
       <c r="W7" s="2"/>
       <c r="X7" s="2"/>
       <c r="Y7" s="2"/>
-      <c r="Z7" s="2"/>
+      <c r="Z7" s="2" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>294</v>
+      </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="G8" s="2" t="s">
+        <v>295</v>
+      </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -1876,9 +1979,13 @@
       <c r="U8" s="2"/>
       <c r="V8" s="2"/>
       <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
+      <c r="X8" s="2" t="s">
+        <v>284</v>
+      </c>
       <c r="Y8" s="2"/>
-      <c r="Z8" s="2"/>
+      <c r="Z8" s="2" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2"/>
@@ -7293,7 +7400,8 @@
     <col width="34" customWidth="1" min="21" max="21" style="16"/>
     <col width="76.6328125" customWidth="1" min="22" max="22" style="16" bestFit="1"/>
     <col width="43.26953125" customWidth="1" min="23" max="23" style="16" bestFit="1"/>
-    <col min="24" max="16384" width="8.7265625" style="16"/>
+    <col min="24" max="24" width="63.1796875" style="16" customWidth="1" bestFit="1"/>
+    <col min="25" max="16384" width="8.7265625" style="16"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" ht="33.75" customFormat="1" s="16">
@@ -7464,7 +7572,7 @@
         <v>107</v>
       </c>
       <c r="O3" s="17" t="s">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="P3" s="17" t="s">
         <v>56</v>
@@ -7517,7 +7625,7 @@
       </c>
       <c r="N4" s="17"/>
       <c r="O4" s="17" t="s">
-        <v>259</v>
+        <v>311</v>
       </c>
       <c r="P4" s="17">
         <v>1</v>
@@ -7538,6 +7646,9 @@
       </c>
       <c r="W4" s="16" t="s">
         <v>281</v>
+      </c>
+      <c r="X4" s="16" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="5" customFormat="1" s="16">
@@ -7676,6 +7787,9 @@
       <c r="W7" s="17" t="s">
         <v>280</v>
       </c>
+      <c r="X7" s="16" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="8" customFormat="1" s="16">
       <c r="A8" s="17" t="s">
@@ -8182,49 +8296,90 @@
       </c>
     </row>
     <row r="18" customFormat="1" s="16">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
+      <c r="A18" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>109</v>
+      </c>
       <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="22"/>
+      <c r="E18" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>287</v>
+      </c>
       <c r="G18" s="22"/>
       <c r="H18" s="17"/>
       <c r="I18" s="22"/>
       <c r="J18" s="22"/>
       <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
+      <c r="L18" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="M18" s="17" t="s">
+        <v>121</v>
+      </c>
       <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
+      <c r="O18" s="17" t="s">
+        <v>310</v>
+      </c>
       <c r="P18" s="17"/>
       <c r="Q18" s="17"/>
-      <c r="R18" s="17"/>
+      <c r="R18" s="17" t="s">
+        <v>214</v>
+      </c>
       <c r="S18" s="17"/>
       <c r="T18" s="17"/>
       <c r="U18" s="17"/>
       <c r="V18" s="17"/>
       <c r="W18" s="17"/>
+      <c r="X18" s="16" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="19" customFormat="1" s="16">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
+      <c r="A19" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>109</v>
+      </c>
       <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="22"/>
+      <c r="E19" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>301</v>
+      </c>
       <c r="G19" s="22"/>
-      <c r="H19" s="17"/>
+      <c r="H19" s="17" t="s">
+        <v>175</v>
+      </c>
       <c r="I19" s="22"/>
       <c r="J19" s="22"/>
       <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
+      <c r="L19" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="M19" s="17" t="s">
+        <v>121</v>
+      </c>
       <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
+      <c r="O19" s="17" t="s">
+        <v>309</v>
+      </c>
       <c r="P19" s="17"/>
       <c r="Q19" s="17"/>
-      <c r="R19" s="17"/>
+      <c r="R19" s="17" t="s">
+        <v>214</v>
+      </c>
       <c r="S19" s="17"/>
       <c r="T19" s="17"/>
       <c r="U19" s="17"/>
@@ -8232,24 +8387,44 @@
       <c r="W19" s="17"/>
     </row>
     <row r="20" customFormat="1" s="16">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
+      <c r="A20" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>109</v>
+      </c>
       <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="22"/>
+      <c r="E20" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>312</v>
+      </c>
       <c r="G20" s="22"/>
-      <c r="H20" s="17"/>
+      <c r="H20" s="17" t="s">
+        <v>175</v>
+      </c>
       <c r="I20" s="22"/>
       <c r="J20" s="22"/>
       <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
+      <c r="L20" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="M20" s="17" t="s">
+        <v>121</v>
+      </c>
       <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
+      <c r="O20" s="17" t="s">
+        <v>308</v>
+      </c>
       <c r="P20" s="17"/>
       <c r="Q20" s="17"/>
-      <c r="R20" s="17"/>
+      <c r="R20" s="17" t="s">
+        <v>214</v>
+      </c>
       <c r="S20" s="17"/>
       <c r="T20" s="17"/>
       <c r="U20" s="17"/>

--- a/data/Genealogie_MEME.xlsx
+++ b/data/Genealogie_MEME.xlsx
@@ -1,18 +1,5 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="75" windowWidth="18195" windowHeight="11820" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1" activeTab="1"/>
-  </bookViews>
-  <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feuille1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registre des personnes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chronologie" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="4" state="visible" r:id="rId4"/>
-  </sheets>
-  <calcPr calcId="171027" fullCalcOnLoad="1"/>
-</workbook>
+<file path=xl/workbook.xml><?xml version="1.0"?><workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><workbookPr/><bookViews><workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="75" windowWidth="18195" windowHeight="11820" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1" activeTab="1"/></bookViews><sheets><sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feuille1" sheetId="1" state="visible" r:id="rId1"/><sheet name="Registre des documents" sheetId="5" r:id="rId8"/><sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registre des personnes" sheetId="2" state="visible" r:id="rId2"/><sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chronologie" sheetId="3" state="visible" r:id="rId3"/><sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="4" state="visible" r:id="rId4"/></sheets><calcPr calcId="171027" fullCalcOnLoad="1"/></workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -955,6 +942,105 @@
   </si>
   <si>
     <t>3 juillet 1913 (batisé)</t>
+  </si>
+  <si>
+    <t>D008</t>
+  </si>
+  <si>
+    <t>D009</t>
+  </si>
+  <si>
+    <t>D010</t>
+  </si>
+  <si>
+    <t>D011</t>
+  </si>
+  <si>
+    <t>D012</t>
+  </si>
+  <si>
+    <t>Liens du doc</t>
+  </si>
+  <si>
+    <t>Livret de famille PEPE-MEME</t>
+  </si>
+  <si>
+    <t>Nom du doc</t>
+  </si>
+  <si>
+    <t>Date du document</t>
+  </si>
+  <si>
+    <t>Tati</t>
+  </si>
+  <si>
+    <t>mariage PEPE et MEME le 6 avril 1934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jean Pierre BERTHOLON; </t>
+  </si>
+  <si>
+    <t>Jean Pierre BERTHOLON; Anna GIRAUD; Cyprien BERTHOLON; Elise LAULAGNIER; François GIRAUD; Joséphine SOLY</t>
+  </si>
+  <si>
+    <t>Autres personnes mentionnées</t>
+  </si>
+  <si>
+    <t>Elise; Simone; Renée; Lucien; Joseph; Andrée; Marc; Gérard</t>
+  </si>
+  <si>
+    <t>carte d'identité Elise LAULAGNIER-BERTHOLON</t>
+  </si>
+  <si>
+    <t>25 janvier 1940</t>
+  </si>
+  <si>
+    <t>6 avril 1934</t>
+  </si>
+  <si>
+    <t>Décé PEPE le 12 juillet 1971; Décé MEME le 12 mars 1994</t>
+  </si>
+  <si>
+    <t>changement de domicile en 1943</t>
+  </si>
+  <si>
+    <t>changement de domicile le 16 avril 1943</t>
+  </si>
+  <si>
+    <t>épouse BERTHOLON</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>livret individuel de guerre Jean BERTHOLON</t>
+  </si>
+  <si>
+    <t>4 septembre 1931</t>
+  </si>
+  <si>
+    <t>changement de domicile le 26 décembre 1938 à UNIAS</t>
+  </si>
+  <si>
+    <t>54éme RAD</t>
+  </si>
+  <si>
+    <t>certificat bonne conduite Cyprien BERTHOLON</t>
+  </si>
+  <si>
+    <t>17 septembre 1906</t>
+  </si>
+  <si>
+    <t>11éme Bataillon de chasseur à pied</t>
+  </si>
+  <si>
+    <t>né le 10 septembre 1882 à St Etienne</t>
+  </si>
+  <si>
+    <t>né le 22 avril 1889</t>
+  </si>
+  <si>
+    <t>né le 22 avril 1889 à St Jeures (haute-Loire)</t>
   </si>
 </sst>
 </file>
@@ -964,7 +1050,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-40C]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1045,6 +1131,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color theme="10"/>
+      <u val="single"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1078,7 +1172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1136,6 +1230,9 @@
     <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="3" applyFill="1" applyAlignment="1" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="12" applyFont="1" xfId="0"/>
+    <xf numFmtId="15" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0"/>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15166,4 +15263,198 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="11.90625" customWidth="1"/>
+    <col min="2" max="2" width="39.1796875" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" width="16.81640625" customWidth="1" bestFit="1" style="27"/>
+    <col min="4" max="4" width="29.7265625" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" width="94.08984375" customWidth="1"/>
+    <col min="6" max="6" width="45.54296875" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" width="17.453125" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" width="49.36328125" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" width="47.7265625" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" width="13.08984375" customWidth="1"/>
+    <col min="11" max="11" width="14.7265625" customWidth="1"/>
+    <col min="12" max="12" width="14.1796875" customWidth="1"/>
+    <col min="13" max="13" width="14.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customHeight="1" ht="27.75">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="E2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F2" t="s">
+        <v>323</v>
+      </c>
+      <c r="G2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H2" t="s">
+        <v>327</v>
+      </c>
+      <c r="I2" t="s">
+        <v>331</v>
+      </c>
+      <c r="M2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="B3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>329</v>
+      </c>
+      <c r="F3" t="s">
+        <v>333</v>
+      </c>
+      <c r="G3" t="s">
+        <v>334</v>
+      </c>
+      <c r="I3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="B4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>337</v>
+      </c>
+      <c r="D4" t="s">
+        <v>339</v>
+      </c>
+      <c r="F4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="B5" t="s">
+        <v>340</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>341</v>
+      </c>
+      <c r="D5" t="s">
+        <v>342</v>
+      </c>
+      <c r="I5" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>317</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" display="D001" r:id="rId1"/>
+    <hyperlink ref="A3" display="D002" r:id="rId2"/>
+    <hyperlink ref="A4" display="D003" r:id="rId3"/>
+    <hyperlink ref="A5" display="D004" r:id="rId4"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/Genealogie_MEME.xlsx
+++ b/data/Genealogie_MEME.xlsx
@@ -1562,9 +1562,7 @@
       <c r="O4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="4" t="s">
-        <v>56</v>
-      </c>
+      <c r="P4" s="4"/>
       <c r="Q4" s="3" t="s">
         <v>57</v>
       </c>
@@ -2631,7 +2629,7 @@
       </c>
       <c r="L29" s="4"/>
       <c r="M29" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N29" s="4" t="s">
         <v>252</v>

--- a/data/Genealogie_MEME.xlsx
+++ b/data/Genealogie_MEME.xlsx
@@ -774,6 +774,15 @@
   </si>
   <si>
     <t>époux d'une tatan du PEPE</t>
+  </si>
+  <si>
+    <t>Simone Cyprienne Victoria</t>
+  </si>
+  <si>
+    <t>Quelle liens avec les autres LAULAGNIER?</t>
+  </si>
+  <si>
+    <t>Quelle liens avec les autres LAULAGNIER? (n'apparait pas dans l'acte notarié donc peu probable fratrie, reste soeur de Francois?</t>
   </si>
 </sst>
 </file>
@@ -1353,7 +1362,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20.08984375" customWidth="1" min="2" max="2" bestFit="1"/>
+    <col width="22.6328125" customWidth="1" min="2" max="2" bestFit="1"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4" bestFit="1"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -1693,7 +1702,7 @@
         <v>157</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>172</v>
+        <v>253</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>30</v>
@@ -2082,7 +2091,9 @@
       <c r="O16" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="P16" s="4"/>
+      <c r="P16" s="4" t="s">
+        <v>255</v>
+      </c>
       <c r="Q16" s="4" t="s">
         <v>63</v>
       </c>

--- a/data/Genealogie_MEME.xlsx
+++ b/data/Genealogie_MEME.xlsx
@@ -783,6 +783,18 @@
   </si>
   <si>
     <t>Quelle liens avec les autres LAULAGNIER? (n'apparait pas dans l'acte notarié donc peu probable fratrie, reste soeur de Francois?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quelle liens avec les autres LAULAGNIER? (n'apparait pas dans l'acte notarié donc peu probable fratrie, reste soeur de Francois? Et Elise est né en 1889, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quelle liens avec les autres LAULAGNIER? (n'apparait pas dans l'acte notarié donc peu probable fratrie, reste soeur de Francois? Et Elise est né en 1889, et si jacques était son père lui est décédé en 1887, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quelle liens avec les autres LAULAGNIER? (n'apparait pas dans l'acte notarié donc peu probable fratrie, reste soeur de Jacques? Et Elise est né en 1889, jacques est décédé en 1887, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Que liens avec les autres LAULAGNIER? (n'apparait pas dans l'acte notarié donc peu probable fratrie, reste soeur de Jacques? Et Elise est né en 1889, Jacques est décédé en 1887, </t>
   </si>
 </sst>
 </file>
@@ -836,7 +848,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -855,6 +867,24 @@
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -868,7 +898,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -888,6 +918,33 @@
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="4" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="5" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="5" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="2" applyFont="1" fillId="5" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="5" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="6" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="6" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="2" applyFont="1" fillId="6" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2053,433 +2110,433 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="s">
+    <row r="16" customFormat="1" s="17">
+      <c r="A16" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="5"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4" t="s">
+      <c r="H16" s="19"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4">
+      <c r="L16" s="18"/>
+      <c r="M16" s="18">
         <v>2</v>
       </c>
-      <c r="N16" s="4" t="s">
+      <c r="N16" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="O16" s="4" t="s">
+      <c r="O16" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="P16" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q16" s="4" t="s">
+      <c r="P16" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q16" s="18" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="s">
+    <row r="17" customFormat="1" s="9">
+      <c r="A17" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4" t="s">
+      <c r="D17" s="10"/>
+      <c r="E17" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="4" t="s">
+      <c r="F17" s="11"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="J17" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4" t="s">
+      <c r="K17" s="10"/>
+      <c r="L17" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="M17" s="4">
+      <c r="M17" s="10">
         <v>2</v>
       </c>
-      <c r="N17" s="4" t="s">
+      <c r="N17" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="O17" s="4" t="s">
+      <c r="O17" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="P17" s="4" t="s">
+      <c r="P17" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="Q17" s="6" t="s">
+      <c r="Q17" s="12" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="s">
+    <row r="18" customFormat="1" s="9">
+      <c r="A18" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4" t="s">
+      <c r="D18" s="10"/>
+      <c r="E18" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="5"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="4" t="s">
+      <c r="F18" s="11"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="J18" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4" t="s">
+      <c r="K18" s="10"/>
+      <c r="L18" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="M18" s="4">
+      <c r="M18" s="10">
         <v>2</v>
       </c>
-      <c r="N18" s="4" t="s">
+      <c r="N18" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="O18" s="4" t="s">
+      <c r="O18" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="P18" s="4" t="s">
+      <c r="P18" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="Q18" s="6" t="s">
+      <c r="Q18" s="12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="s">
+    <row r="19" customFormat="1" s="9">
+      <c r="A19" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4" t="s">
+      <c r="D19" s="10"/>
+      <c r="E19" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="5"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="4" t="s">
+      <c r="F19" s="11"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="J19" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4" t="s">
+      <c r="K19" s="10"/>
+      <c r="L19" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="M19" s="4">
+      <c r="M19" s="10">
         <v>2</v>
       </c>
-      <c r="N19" s="4" t="s">
+      <c r="N19" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="O19" s="4" t="s">
+      <c r="O19" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="P19" s="4" t="s">
+      <c r="P19" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="Q19" s="6" t="s">
+      <c r="Q19" s="12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="s">
+    <row r="20" customFormat="1" s="9">
+      <c r="A20" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4" t="s">
+      <c r="D20" s="10"/>
+      <c r="E20" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="4" t="s">
+      <c r="F20" s="11"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J20" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4" t="s">
+      <c r="K20" s="10"/>
+      <c r="L20" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="M20" s="4">
+      <c r="M20" s="10">
         <v>2</v>
       </c>
-      <c r="N20" s="4" t="s">
+      <c r="N20" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="O20" s="4" t="s">
+      <c r="O20" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="P20" s="4" t="s">
+      <c r="P20" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="Q20" s="6" t="s">
+      <c r="Q20" s="12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="s">
+    <row r="21" customFormat="1" s="9">
+      <c r="A21" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4" t="s">
+      <c r="D21" s="10"/>
+      <c r="E21" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="4" t="s">
+      <c r="F21" s="11"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="J21" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4" t="s">
+      <c r="K21" s="10"/>
+      <c r="L21" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="M21" s="4">
+      <c r="M21" s="10">
         <v>2</v>
       </c>
-      <c r="N21" s="4" t="s">
+      <c r="N21" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="O21" s="4" t="s">
+      <c r="O21" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="P21" s="4" t="s">
+      <c r="P21" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="Q21" s="6" t="s">
+      <c r="Q21" s="12" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="s">
+    <row r="22" customFormat="1" s="9">
+      <c r="A22" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F22" s="5"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="4" t="s">
+      <c r="F22" s="11"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="J22" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="K22" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="L22" s="4" t="s">
+      <c r="L22" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="M22" s="4">
+      <c r="M22" s="10">
         <v>2</v>
       </c>
-      <c r="N22" s="4" t="s">
+      <c r="N22" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="O22" s="4" t="s">
+      <c r="O22" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="P22" s="4" t="s">
+      <c r="P22" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="Q22" s="6" t="s">
+      <c r="Q22" s="12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="s">
+    <row r="23" customFormat="1" s="9">
+      <c r="A23" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4" t="s">
+      <c r="D23" s="10"/>
+      <c r="E23" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="5"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="5" t="s">
+      <c r="F23" s="11"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="J23" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4" t="s">
+      <c r="K23" s="10"/>
+      <c r="L23" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="M23" s="4">
+      <c r="M23" s="10">
         <v>2</v>
       </c>
-      <c r="N23" s="4" t="s">
+      <c r="N23" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="O23" s="4" t="s">
+      <c r="O23" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="P23" s="4" t="s">
+      <c r="P23" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="Q23" s="6" t="s">
+      <c r="Q23" s="12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="s">
+    <row r="24" customFormat="1" s="13">
+      <c r="A24" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4" t="s">
+      <c r="D24" s="14"/>
+      <c r="E24" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="5" t="s">
+      <c r="F24" s="15"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4" t="s">
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4">
+      <c r="L24" s="14"/>
+      <c r="M24" s="14">
         <v>3</v>
       </c>
-      <c r="N24" s="4" t="s">
+      <c r="N24" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="O24" s="4" t="s">
+      <c r="O24" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="6" t="s">
+      <c r="P24" s="14"/>
+      <c r="Q24" s="16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="s">
+    <row r="25" customFormat="1" s="13">
+      <c r="A25" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4" t="s">
+      <c r="D25" s="14"/>
+      <c r="E25" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="5" t="s">
+      <c r="F25" s="15"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4" t="s">
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4">
+      <c r="L25" s="14"/>
+      <c r="M25" s="14">
         <v>3</v>
       </c>
-      <c r="N25" s="4" t="s">
+      <c r="N25" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="O25" s="4" t="s">
+      <c r="O25" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="P25" s="4"/>
-      <c r="Q25" s="6" t="s">
+      <c r="P25" s="14"/>
+      <c r="Q25" s="16" t="s">
         <v>63</v>
       </c>
     </row>

--- a/data/Genealogie_MEME.xlsx
+++ b/data/Genealogie_MEME.xlsx
@@ -796,13 +796,64 @@
   <si>
     <t xml:space="preserve">Que liens avec les autres LAULAGNIER? (n'apparait pas dans l'acte notarié donc peu probable fratrie, reste soeur de Jacques? Et Elise est né en 1889, Jacques est décédé en 1887, </t>
   </si>
+  <si>
+    <t>Que liens avec les autres LAULAGNIER? (n'apparait pas dans l'acte notarié donc peu probable fratrie, et Elise est né en 1889, Jacques est décédé en 1887, soit 2 ans avant.</t>
+  </si>
+  <si>
+    <t>Que liens avec les autres LAULAGNIER? (n'apparait pas dans l'acte notarié donc peu probable fratrie, et Elise est né en 1889, Jacques est décédé en 1887, soit 2 ans avant. Reste Elise serait la nièce de Jacques (Jacques à une fraterie et sa soeur/frère aurait eu Elise en 1889) OU Elise serait la petite nièce de Jacques ( si Jacque est né entre 1830 et 1840, alors Jacques pourrait-être le frère du grand père d'Elise) OU Jacques pourrait être le cousin d'un parent d'Elise donc Elise serait une cousine au 2ème degré.</t>
+  </si>
+  <si>
+    <t>act naissance Elise LAULAGNIER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P021; </t>
+  </si>
+  <si>
+    <t>Archive43</t>
+  </si>
+  <si>
+    <t>P035</t>
+  </si>
+  <si>
+    <t>Pierre</t>
+  </si>
+  <si>
+    <t>en 1853</t>
+  </si>
+  <si>
+    <t>P036</t>
+  </si>
+  <si>
+    <t>Rose</t>
+  </si>
+  <si>
+    <t>PEYRACHON</t>
+  </si>
+  <si>
+    <t>en 1855</t>
+  </si>
+  <si>
+    <t>?? Charbonnière</t>
+  </si>
+  <si>
+    <t>P021;P035;P036</t>
+  </si>
+  <si>
+    <t>avril 1889</t>
+  </si>
+  <si>
+    <t>parent de Elise maman du PEPE</t>
+  </si>
+  <si>
+    <t>Grand parent Maternel du PEPE</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -847,8 +898,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="FFFAC090"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <color rgb="FFFAC090"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -885,6 +951,12 @@
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAC090"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -898,7 +970,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -943,6 +1015,34 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" applyNumberFormat="1" fontId="2" applyFont="1" fillId="6" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="6" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="6" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="7" applyFont="1" fillId="6" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="6" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="6" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="3" applyFont="1" fillId="6" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="7" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="7" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="3" applyFont="1" fillId="7" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="7" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="7" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="2" applyFont="1" fillId="7" applyFill="1" applyAlignment="1" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2110,48 +2210,52 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" customFormat="1" s="17">
-      <c r="A16" s="18" t="s">
+    <row r="16" customFormat="1" s="26">
+      <c r="A16" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="19"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18" t="s">
+      <c r="H16" s="28"/>
+      <c r="I16" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="J16" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="K16" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="L16" s="18"/>
-      <c r="M16" s="18">
+      <c r="L16" s="27"/>
+      <c r="M16" s="27">
         <v>2</v>
       </c>
-      <c r="N16" s="18" t="s">
+      <c r="N16" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="O16" s="18" t="s">
+      <c r="O16" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="P16" s="18" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q16" s="18" t="s">
+      <c r="P16" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q16" s="27" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2229,7 +2333,7 @@
         <v>2</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="O18" s="10" t="s">
         <v>55</v>
@@ -2710,43 +2814,85 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="4"/>
+    <row r="30" customFormat="1" s="29">
+      <c r="A30" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="B30" s="30" t="s">
+        <v>266</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" s="31" t="s">
+        <v>267</v>
+      </c>
+      <c r="G30" s="30"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30">
+        <v>3</v>
+      </c>
+      <c r="N30" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="O30" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="P30" s="30"/>
+      <c r="Q30" s="27" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" s="29">
+      <c r="A31" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="B31" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="C31" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="E31" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="F31" s="31" t="s">
+        <v>271</v>
+      </c>
+      <c r="G31" s="30"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30">
+        <v>3</v>
+      </c>
+      <c r="N31" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="O31" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="P31" s="30"/>
+      <c r="Q31" s="27" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4"/>
@@ -8429,10 +8575,21 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="s">
+      <c r="A19" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="C19" s="2"/>
+      <c r="B19" t="s">
+        <v>262</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D19" t="s">
+        <v>273</v>
+      </c>
+      <c r="E19" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -9899,6 +10056,7 @@
     <hyperlink ref="A16" display="D015" r:id="rId15"/>
     <hyperlink ref="A17" display="D016" r:id="rId16"/>
     <hyperlink ref="A18" display="D017" r:id="rId17"/>
+    <hyperlink ref="A19" display="D018" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
